--- a/past_data/site_8023/2026-08-01.xlsx
+++ b/past_data/site_8023/2026-08-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="48">
   <si>
     <t>No.</t>
   </si>
@@ -35,25 +35,43 @@
     <t>평균</t>
   </si>
   <si>
-    <t>452.4</t>
+    <t>464.2</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
+    <t>4.6</t>
+  </si>
+  <si>
+    <t>01일</t>
+  </si>
+  <si>
+    <t>453.6</t>
+  </si>
+  <si>
     <t>4.5</t>
   </si>
   <si>
-    <t>01일</t>
-  </si>
-  <si>
     <t>02일</t>
   </si>
   <si>
+    <t>474.8</t>
+  </si>
+  <si>
+    <t>928.4</t>
+  </si>
+  <si>
+    <t>4.7</t>
+  </si>
+  <si>
+    <t>9.3</t>
+  </si>
+  <si>
+    <t>03일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>03일</t>
   </si>
   <si>
     <t>04일</t>
@@ -448,16 +466,16 @@
         <v>10</v>
       </c>
       <c r="C3" t="s" s="31">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D3" t="s" s="32">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E3" t="s" s="33">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F3" t="s" s="34">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" ht="17.25" customHeight="1">
@@ -465,19 +483,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s" s="35">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s" s="36">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D4" t="s" s="37">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E4" t="s" s="38">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F4" t="s" s="39">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" ht="17.25" customHeight="1">
@@ -485,19 +503,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s" s="30">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D5" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E5" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F5" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" ht="17.25" customHeight="1">
@@ -505,19 +523,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s" s="35">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C6" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D6" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E6" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F6" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" ht="17.25" customHeight="1">
@@ -525,19 +543,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s" s="30">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C7" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D7" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E7" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F7" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" ht="17.25" customHeight="1">
@@ -545,19 +563,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s" s="35">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C8" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D8" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E8" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F8" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" ht="17.25" customHeight="1">
@@ -565,19 +583,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s" s="30">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C9" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D9" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E9" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F9" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1">
@@ -585,19 +603,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s" s="35">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C10" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D10" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E10" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F10" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1">
@@ -605,19 +623,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s" s="30">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C11" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D11" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E11" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F11" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -625,19 +643,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C12" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D12" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E12" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F12" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -645,19 +663,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C13" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -665,19 +683,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -685,19 +703,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -705,19 +723,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -725,19 +743,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -745,19 +763,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -765,19 +783,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -785,19 +803,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -805,19 +823,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -825,19 +843,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -845,19 +863,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -865,19 +883,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -885,19 +903,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -905,19 +923,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -925,19 +943,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -945,19 +963,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -965,19 +983,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -985,19 +1003,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1005,19 +1023,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1025,19 +1043,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1045,19 +1063,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-08-01.xlsx
+++ b/past_data/site_8023/2026-08-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="51">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>464.2</t>
+    <t>481.7</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>4.6</t>
+    <t>4.8</t>
   </si>
   <si>
     <t>01일</t>
@@ -56,13 +56,10 @@
     <t>02일</t>
   </si>
   <si>
-    <t>474.8</t>
-  </si>
-  <si>
-    <t>928.4</t>
-  </si>
-  <si>
-    <t>4.7</t>
+    <t>475.8</t>
+  </si>
+  <si>
+    <t>929.4</t>
   </si>
   <si>
     <t>9.3</t>
@@ -71,10 +68,22 @@
     <t>03일</t>
   </si>
   <si>
+    <t>515.6</t>
+  </si>
+  <si>
+    <t>1445.0</t>
+  </si>
+  <si>
+    <t>5.2</t>
+  </si>
+  <si>
+    <t>14.5</t>
+  </si>
+  <si>
+    <t>04일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>04일</t>
   </si>
   <si>
     <t>05일</t>
@@ -492,10 +501,10 @@
         <v>15</v>
       </c>
       <c r="E4" t="s" s="38">
+        <v>9</v>
+      </c>
+      <c r="F4" t="s" s="39">
         <v>16</v>
-      </c>
-      <c r="F4" t="s" s="39">
-        <v>17</v>
       </c>
     </row>
     <row r="5" ht="17.25" customHeight="1">
@@ -503,19 +512,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s" s="30">
+        <v>17</v>
+      </c>
+      <c r="C5" t="s" s="31">
         <v>18</v>
-      </c>
-      <c r="C5" t="s" s="31">
-        <v>19</v>
       </c>
       <c r="D5" t="s" s="32">
         <v>19</v>
       </c>
       <c r="E5" t="s" s="33">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F5" t="s" s="34">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" ht="17.25" customHeight="1">
@@ -523,19 +532,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s" s="35">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C6" t="s" s="36">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D6" t="s" s="37">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E6" t="s" s="38">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F6" t="s" s="39">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" ht="17.25" customHeight="1">
@@ -543,19 +552,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s" s="30">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C7" t="s" s="31">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D7" t="s" s="32">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E7" t="s" s="33">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F7" t="s" s="34">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" ht="17.25" customHeight="1">
@@ -563,19 +572,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s" s="35">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C8" t="s" s="36">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D8" t="s" s="37">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E8" t="s" s="38">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F8" t="s" s="39">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" ht="17.25" customHeight="1">
@@ -583,19 +592,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s" s="30">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C9" t="s" s="31">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D9" t="s" s="32">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E9" t="s" s="33">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F9" t="s" s="34">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1">
@@ -603,19 +612,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s" s="35">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C10" t="s" s="36">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D10" t="s" s="37">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E10" t="s" s="38">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F10" t="s" s="39">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1">
@@ -623,19 +632,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s" s="30">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C11" t="s" s="31">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D11" t="s" s="32">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E11" t="s" s="33">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F11" t="s" s="34">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -643,19 +652,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C12" t="s" s="36">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D12" t="s" s="37">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E12" t="s" s="38">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F12" t="s" s="39">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -663,19 +672,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C13" t="s" s="31">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -683,19 +692,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -703,19 +712,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -723,19 +732,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -743,19 +752,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -763,19 +772,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -783,19 +792,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -803,19 +812,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -823,19 +832,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -843,19 +852,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -863,19 +872,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -883,19 +892,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -903,19 +912,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -923,19 +932,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -943,19 +952,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -963,19 +972,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -983,19 +992,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1003,19 +1012,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1023,19 +1032,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1043,19 +1052,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1063,19 +1072,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-08-01.xlsx
+++ b/past_data/site_8023/2026-08-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="56">
   <si>
     <t>No.</t>
   </si>
@@ -35,33 +35,36 @@
     <t>평균</t>
   </si>
   <si>
-    <t>481.7</t>
+    <t>495.6</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
+    <t>5.0</t>
+  </si>
+  <si>
+    <t>01일</t>
+  </si>
+  <si>
+    <t>453.6</t>
+  </si>
+  <si>
+    <t>4.5</t>
+  </si>
+  <si>
+    <t>02일</t>
+  </si>
+  <si>
+    <t>475.8</t>
+  </si>
+  <si>
+    <t>929.4</t>
+  </si>
+  <si>
     <t>4.8</t>
   </si>
   <si>
-    <t>01일</t>
-  </si>
-  <si>
-    <t>453.6</t>
-  </si>
-  <si>
-    <t>4.5</t>
-  </si>
-  <si>
-    <t>02일</t>
-  </si>
-  <si>
-    <t>475.8</t>
-  </si>
-  <si>
-    <t>929.4</t>
-  </si>
-  <si>
     <t>9.3</t>
   </si>
   <si>
@@ -83,10 +86,22 @@
     <t>04일</t>
   </si>
   <si>
+    <t>537.3</t>
+  </si>
+  <si>
+    <t>1982.3</t>
+  </si>
+  <si>
+    <t>5.4</t>
+  </si>
+  <si>
+    <t>19.8</t>
+  </si>
+  <si>
+    <t>05일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>05일</t>
   </si>
   <si>
     <t>06일</t>
@@ -501,10 +516,10 @@
         <v>15</v>
       </c>
       <c r="E4" t="s" s="38">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="F4" t="s" s="39">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" ht="17.25" customHeight="1">
@@ -512,19 +527,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s" s="30">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s" s="31">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D5" t="s" s="32">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E5" t="s" s="33">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F5" t="s" s="34">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" ht="17.25" customHeight="1">
@@ -532,19 +547,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s" s="35">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s" s="36">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D6" t="s" s="37">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E6" t="s" s="38">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F6" t="s" s="39">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" ht="17.25" customHeight="1">
@@ -552,19 +567,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s" s="30">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C7" t="s" s="31">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D7" t="s" s="32">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E7" t="s" s="33">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F7" t="s" s="34">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" ht="17.25" customHeight="1">
@@ -572,19 +587,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s" s="35">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C8" t="s" s="36">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D8" t="s" s="37">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E8" t="s" s="38">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F8" t="s" s="39">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" ht="17.25" customHeight="1">
@@ -592,19 +607,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s" s="30">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C9" t="s" s="31">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D9" t="s" s="32">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E9" t="s" s="33">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F9" t="s" s="34">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1">
@@ -612,19 +627,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s" s="35">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C10" t="s" s="36">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D10" t="s" s="37">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E10" t="s" s="38">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F10" t="s" s="39">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1">
@@ -632,19 +647,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s" s="30">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C11" t="s" s="31">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D11" t="s" s="32">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E11" t="s" s="33">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F11" t="s" s="34">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -652,19 +667,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C12" t="s" s="36">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D12" t="s" s="37">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E12" t="s" s="38">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F12" t="s" s="39">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -672,19 +687,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C13" t="s" s="31">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -692,19 +707,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -712,19 +727,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -732,19 +747,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -752,19 +767,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -772,19 +787,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -792,19 +807,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -812,19 +827,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -832,19 +847,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -852,19 +867,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -872,19 +887,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -892,19 +907,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -912,19 +927,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -932,19 +947,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -952,19 +967,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -972,19 +987,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -992,19 +1007,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1012,19 +1027,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1032,19 +1047,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1052,19 +1067,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1072,19 +1087,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-08-01.xlsx
+++ b/past_data/site_8023/2026-08-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="59">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>495.6</t>
+    <t>494.4</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>5.0</t>
+    <t>4.9</t>
   </si>
   <si>
     <t>01일</t>
@@ -101,10 +101,19 @@
     <t>05일</t>
   </si>
   <si>
+    <t>489.8</t>
+  </si>
+  <si>
+    <t>2472.1</t>
+  </si>
+  <si>
+    <t>24.7</t>
+  </si>
+  <si>
+    <t>06일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>06일</t>
   </si>
   <si>
     <t>07일</t>
@@ -573,13 +582,13 @@
         <v>29</v>
       </c>
       <c r="D7" t="s" s="32">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E7" t="s" s="33">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s" s="34">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" ht="17.25" customHeight="1">
@@ -587,19 +596,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s" s="35">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C8" t="s" s="36">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D8" t="s" s="37">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E8" t="s" s="38">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F8" t="s" s="39">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" ht="17.25" customHeight="1">
@@ -607,19 +616,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s" s="30">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C9" t="s" s="31">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D9" t="s" s="32">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E9" t="s" s="33">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F9" t="s" s="34">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1">
@@ -627,19 +636,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s" s="35">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C10" t="s" s="36">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D10" t="s" s="37">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E10" t="s" s="38">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F10" t="s" s="39">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1">
@@ -647,19 +656,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s" s="30">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C11" t="s" s="31">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D11" t="s" s="32">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E11" t="s" s="33">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F11" t="s" s="34">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -667,19 +676,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C12" t="s" s="36">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D12" t="s" s="37">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E12" t="s" s="38">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F12" t="s" s="39">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -687,19 +696,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C13" t="s" s="31">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -707,19 +716,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -727,19 +736,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -747,19 +756,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -767,19 +776,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -787,19 +796,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -807,19 +816,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -827,19 +836,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -847,19 +856,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -867,19 +876,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -887,19 +896,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -907,19 +916,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -927,19 +936,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -947,19 +956,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -967,19 +976,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -987,19 +996,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1007,19 +1016,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1027,19 +1036,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1047,19 +1056,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1067,19 +1076,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1087,19 +1096,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-08-01.xlsx
+++ b/past_data/site_8023/2026-08-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="63">
   <si>
     <t>No.</t>
   </si>
@@ -35,88 +35,100 @@
     <t>평균</t>
   </si>
   <si>
-    <t>494.4</t>
+    <t>502.0</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
+    <t>5.0</t>
+  </si>
+  <si>
+    <t>01일</t>
+  </si>
+  <si>
+    <t>453.6</t>
+  </si>
+  <si>
+    <t>4.5</t>
+  </si>
+  <si>
+    <t>02일</t>
+  </si>
+  <si>
+    <t>475.8</t>
+  </si>
+  <si>
+    <t>929.4</t>
+  </si>
+  <si>
+    <t>4.8</t>
+  </si>
+  <si>
+    <t>9.3</t>
+  </si>
+  <si>
+    <t>03일</t>
+  </si>
+  <si>
+    <t>515.6</t>
+  </si>
+  <si>
+    <t>1445.0</t>
+  </si>
+  <si>
+    <t>5.2</t>
+  </si>
+  <si>
+    <t>14.5</t>
+  </si>
+  <si>
+    <t>04일</t>
+  </si>
+  <si>
+    <t>537.3</t>
+  </si>
+  <si>
+    <t>1982.3</t>
+  </si>
+  <si>
+    <t>5.4</t>
+  </si>
+  <si>
+    <t>19.8</t>
+  </si>
+  <si>
+    <t>05일</t>
+  </si>
+  <si>
+    <t>489.8</t>
+  </si>
+  <si>
+    <t>2472.1</t>
+  </si>
+  <si>
     <t>4.9</t>
   </si>
   <si>
-    <t>01일</t>
-  </si>
-  <si>
-    <t>453.6</t>
-  </si>
-  <si>
-    <t>4.5</t>
-  </si>
-  <si>
-    <t>02일</t>
-  </si>
-  <si>
-    <t>475.8</t>
-  </si>
-  <si>
-    <t>929.4</t>
-  </si>
-  <si>
-    <t>4.8</t>
-  </si>
-  <si>
-    <t>9.3</t>
-  </si>
-  <si>
-    <t>03일</t>
-  </si>
-  <si>
-    <t>515.6</t>
-  </si>
-  <si>
-    <t>1445.0</t>
-  </si>
-  <si>
-    <t>5.2</t>
-  </si>
-  <si>
-    <t>14.5</t>
-  </si>
-  <si>
-    <t>04일</t>
-  </si>
-  <si>
-    <t>537.3</t>
-  </si>
-  <si>
-    <t>1982.3</t>
-  </si>
-  <si>
-    <t>5.4</t>
-  </si>
-  <si>
-    <t>19.8</t>
-  </si>
-  <si>
-    <t>05일</t>
-  </si>
-  <si>
-    <t>489.8</t>
-  </si>
-  <si>
-    <t>2472.1</t>
-  </si>
-  <si>
     <t>24.7</t>
   </si>
   <si>
     <t>06일</t>
   </si>
   <si>
+    <t>540.1</t>
+  </si>
+  <si>
+    <t>3012.2</t>
+  </si>
+  <si>
+    <t>30.1</t>
+  </si>
+  <si>
+    <t>07일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>07일</t>
   </si>
   <si>
     <t>08일</t>
@@ -585,10 +597,10 @@
         <v>30</v>
       </c>
       <c r="E7" t="s" s="33">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="F7" t="s" s="34">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" ht="17.25" customHeight="1">
@@ -596,19 +608,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s" s="35">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C8" t="s" s="36">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s" s="37">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E8" t="s" s="38">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F8" t="s" s="39">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" ht="17.25" customHeight="1">
@@ -616,19 +628,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s" s="30">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C9" t="s" s="31">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D9" t="s" s="32">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E9" t="s" s="33">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F9" t="s" s="34">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1">
@@ -636,19 +648,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s" s="35">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C10" t="s" s="36">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D10" t="s" s="37">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E10" t="s" s="38">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F10" t="s" s="39">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1">
@@ -656,19 +668,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s" s="30">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C11" t="s" s="31">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D11" t="s" s="32">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E11" t="s" s="33">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F11" t="s" s="34">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -676,19 +688,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C12" t="s" s="36">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D12" t="s" s="37">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E12" t="s" s="38">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F12" t="s" s="39">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -696,19 +708,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C13" t="s" s="31">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -716,19 +728,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -736,19 +748,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -756,19 +768,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -776,19 +788,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -796,19 +808,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -816,19 +828,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -836,19 +848,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -856,19 +868,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -876,19 +888,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -896,19 +908,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -916,19 +928,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -936,19 +948,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -956,19 +968,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -976,19 +988,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -996,19 +1008,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1016,19 +1028,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1036,19 +1048,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1056,19 +1068,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1076,19 +1088,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1096,19 +1108,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-08-01.xlsx
+++ b/past_data/site_8023/2026-08-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="66">
   <si>
     <t>No.</t>
   </si>
@@ -35,7 +35,7 @@
     <t>평균</t>
   </si>
   <si>
-    <t>502.0</t>
+    <t>504.0</t>
   </si>
   <si>
     <t>-</t>
@@ -128,10 +128,19 @@
     <t>07일</t>
   </si>
   <si>
+    <t>516.0</t>
+  </si>
+  <si>
+    <t>3528.2</t>
+  </si>
+  <si>
+    <t>35.3</t>
+  </si>
+  <si>
+    <t>08일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>08일</t>
   </si>
   <si>
     <t>09일</t>
@@ -634,13 +643,13 @@
         <v>38</v>
       </c>
       <c r="D9" t="s" s="32">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E9" t="s" s="33">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="F9" t="s" s="34">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1">
@@ -648,19 +657,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s" s="35">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C10" t="s" s="36">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D10" t="s" s="37">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E10" t="s" s="38">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F10" t="s" s="39">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1">
@@ -668,19 +677,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s" s="30">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C11" t="s" s="31">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D11" t="s" s="32">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E11" t="s" s="33">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F11" t="s" s="34">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -688,19 +697,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C12" t="s" s="36">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D12" t="s" s="37">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E12" t="s" s="38">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F12" t="s" s="39">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -708,19 +717,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C13" t="s" s="31">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -728,19 +737,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -748,19 +757,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -768,19 +777,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -788,19 +797,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -808,19 +817,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -828,19 +837,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -848,19 +857,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -868,19 +877,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -888,19 +897,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -908,19 +917,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -928,19 +937,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -948,19 +957,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -968,19 +977,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -988,19 +997,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1008,19 +1017,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1028,19 +1037,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1048,19 +1057,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1068,19 +1077,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1088,19 +1097,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1108,19 +1117,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-08-01.xlsx
+++ b/past_data/site_8023/2026-08-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="70">
   <si>
     <t>No.</t>
   </si>
@@ -35,7 +35,7 @@
     <t>평균</t>
   </si>
   <si>
-    <t>504.0</t>
+    <t>500.9</t>
   </si>
   <si>
     <t>-</t>
@@ -128,22 +128,34 @@
     <t>07일</t>
   </si>
   <si>
-    <t>516.0</t>
-  </si>
-  <si>
-    <t>3528.2</t>
-  </si>
-  <si>
-    <t>35.3</t>
+    <t>523.4</t>
+  </si>
+  <si>
+    <t>3535.6</t>
+  </si>
+  <si>
+    <t>35.4</t>
   </si>
   <si>
     <t>08일</t>
   </si>
   <si>
+    <t>471.9</t>
+  </si>
+  <si>
+    <t>4007.5</t>
+  </si>
+  <si>
+    <t>4.7</t>
+  </si>
+  <si>
+    <t>40.1</t>
+  </si>
+  <si>
+    <t>09일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>09일</t>
   </si>
   <si>
     <t>10일</t>
@@ -663,13 +675,13 @@
         <v>42</v>
       </c>
       <c r="D10" t="s" s="37">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E10" t="s" s="38">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F10" t="s" s="39">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1">
@@ -677,19 +689,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s" s="30">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C11" t="s" s="31">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D11" t="s" s="32">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E11" t="s" s="33">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F11" t="s" s="34">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -697,19 +709,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C12" t="s" s="36">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D12" t="s" s="37">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E12" t="s" s="38">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F12" t="s" s="39">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -717,19 +729,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C13" t="s" s="31">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -737,19 +749,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -757,19 +769,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -777,19 +789,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -797,19 +809,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -817,19 +829,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -837,19 +849,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -857,19 +869,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -877,19 +889,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -897,19 +909,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -917,19 +929,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -937,19 +949,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -957,19 +969,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -977,19 +989,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -997,19 +1009,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1017,19 +1029,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1037,19 +1049,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1057,19 +1069,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1077,19 +1089,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1097,19 +1109,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1117,19 +1129,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-08-01.xlsx
+++ b/past_data/site_8023/2026-08-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="72">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>500.9</t>
+    <t>488.9</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>5.0</t>
+    <t>4.9</t>
   </si>
   <si>
     <t>01일</t>
@@ -107,9 +107,6 @@
     <t>2472.1</t>
   </si>
   <si>
-    <t>4.9</t>
-  </si>
-  <si>
     <t>24.7</t>
   </si>
   <si>
@@ -140,25 +137,34 @@
     <t>08일</t>
   </si>
   <si>
-    <t>471.9</t>
-  </si>
-  <si>
-    <t>4007.5</t>
-  </si>
-  <si>
-    <t>4.7</t>
-  </si>
-  <si>
-    <t>40.1</t>
+    <t>482.2</t>
+  </si>
+  <si>
+    <t>4017.8</t>
+  </si>
+  <si>
+    <t>40.2</t>
   </si>
   <si>
     <t>09일</t>
   </si>
   <si>
+    <t>381.9</t>
+  </si>
+  <si>
+    <t>4399.7</t>
+  </si>
+  <si>
+    <t>3.8</t>
+  </si>
+  <si>
+    <t>44.0</t>
+  </si>
+  <si>
+    <t>10일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>10일</t>
   </si>
   <si>
     <t>11일</t>
@@ -618,10 +624,10 @@
         <v>30</v>
       </c>
       <c r="E7" t="s" s="33">
+        <v>9</v>
+      </c>
+      <c r="F7" t="s" s="34">
         <v>31</v>
-      </c>
-      <c r="F7" t="s" s="34">
-        <v>32</v>
       </c>
     </row>
     <row r="8" ht="17.25" customHeight="1">
@@ -629,19 +635,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s" s="35">
+        <v>32</v>
+      </c>
+      <c r="C8" t="s" s="36">
         <v>33</v>
       </c>
-      <c r="C8" t="s" s="36">
+      <c r="D8" t="s" s="37">
         <v>34</v>
-      </c>
-      <c r="D8" t="s" s="37">
-        <v>35</v>
       </c>
       <c r="E8" t="s" s="38">
         <v>26</v>
       </c>
       <c r="F8" t="s" s="39">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" ht="17.25" customHeight="1">
@@ -649,19 +655,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s" s="30">
+        <v>36</v>
+      </c>
+      <c r="C9" t="s" s="31">
         <v>37</v>
       </c>
-      <c r="C9" t="s" s="31">
+      <c r="D9" t="s" s="32">
         <v>38</v>
-      </c>
-      <c r="D9" t="s" s="32">
-        <v>39</v>
       </c>
       <c r="E9" t="s" s="33">
         <v>21</v>
       </c>
       <c r="F9" t="s" s="34">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1">
@@ -669,19 +675,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s" s="35">
+        <v>40</v>
+      </c>
+      <c r="C10" t="s" s="36">
         <v>41</v>
       </c>
-      <c r="C10" t="s" s="36">
+      <c r="D10" t="s" s="37">
         <v>42</v>
       </c>
-      <c r="D10" t="s" s="37">
+      <c r="E10" t="s" s="38">
+        <v>16</v>
+      </c>
+      <c r="F10" t="s" s="39">
         <v>43</v>
-      </c>
-      <c r="E10" t="s" s="38">
-        <v>44</v>
-      </c>
-      <c r="F10" t="s" s="39">
-        <v>45</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1">
@@ -689,19 +695,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s" s="30">
+        <v>44</v>
+      </c>
+      <c r="C11" t="s" s="31">
+        <v>45</v>
+      </c>
+      <c r="D11" t="s" s="32">
         <v>46</v>
-      </c>
-      <c r="C11" t="s" s="31">
-        <v>47</v>
-      </c>
-      <c r="D11" t="s" s="32">
-        <v>47</v>
       </c>
       <c r="E11" t="s" s="33">
         <v>47</v>
       </c>
       <c r="F11" t="s" s="34">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -709,19 +715,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C12" t="s" s="36">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D12" t="s" s="37">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E12" t="s" s="38">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F12" t="s" s="39">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -729,19 +735,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C13" t="s" s="31">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -749,19 +755,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -769,19 +775,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -789,19 +795,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -809,19 +815,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -829,19 +835,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -849,19 +855,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -869,19 +875,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -889,19 +895,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -909,19 +915,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -929,19 +935,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -949,19 +955,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -969,19 +975,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -989,19 +995,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1009,19 +1015,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1029,19 +1035,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1049,19 +1055,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1069,19 +1075,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1089,19 +1095,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1109,19 +1115,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1129,19 +1135,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-08-01.xlsx
+++ b/past_data/site_8023/2026-08-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="76">
   <si>
     <t>No.</t>
   </si>
@@ -35,7 +35,7 @@
     <t>평균</t>
   </si>
   <si>
-    <t>488.9</t>
+    <t>486.6</t>
   </si>
   <si>
     <t>-</t>
@@ -149,25 +149,37 @@
     <t>09일</t>
   </si>
   <si>
-    <t>381.9</t>
-  </si>
-  <si>
-    <t>4399.7</t>
-  </si>
-  <si>
-    <t>3.8</t>
-  </si>
-  <si>
-    <t>44.0</t>
+    <t>392.0</t>
+  </si>
+  <si>
+    <t>4409.8</t>
+  </si>
+  <si>
+    <t>3.9</t>
+  </si>
+  <si>
+    <t>44.1</t>
   </si>
   <si>
     <t>10일</t>
   </si>
   <si>
+    <t>456.3</t>
+  </si>
+  <si>
+    <t>4866.1</t>
+  </si>
+  <si>
+    <t>4.6</t>
+  </si>
+  <si>
+    <t>48.7</t>
+  </si>
+  <si>
+    <t>11일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>11일</t>
   </si>
   <si>
     <t>12일</t>
@@ -721,13 +733,13 @@
         <v>50</v>
       </c>
       <c r="D12" t="s" s="37">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E12" t="s" s="38">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F12" t="s" s="39">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -735,19 +747,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C13" t="s" s="31">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>50</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -755,19 +767,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>50</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -775,19 +787,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>50</v>
+        <v>55</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -795,19 +807,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>50</v>
+        <v>55</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -815,19 +827,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>50</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -835,19 +847,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>50</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -855,19 +867,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>50</v>
+        <v>55</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -875,19 +887,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>50</v>
+        <v>55</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -895,19 +907,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>50</v>
+        <v>55</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -915,19 +927,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>50</v>
+        <v>55</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -935,19 +947,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>50</v>
+        <v>55</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -955,19 +967,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>50</v>
+        <v>55</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -975,19 +987,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>50</v>
+        <v>55</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -995,19 +1007,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>50</v>
+        <v>55</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1015,19 +1027,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>50</v>
+        <v>55</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1035,19 +1047,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>50</v>
+        <v>55</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1055,19 +1067,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>50</v>
+        <v>55</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1075,19 +1087,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>50</v>
+        <v>55</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1095,19 +1107,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>50</v>
+        <v>55</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1115,19 +1127,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>50</v>
+        <v>55</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1135,19 +1147,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>50</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-08-01.xlsx
+++ b/past_data/site_8023/2026-08-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="80">
   <si>
     <t>No.</t>
   </si>
@@ -35,7 +35,7 @@
     <t>평균</t>
   </si>
   <si>
-    <t>486.6</t>
+    <t>485.6</t>
   </si>
   <si>
     <t>-</t>
@@ -164,10 +164,10 @@
     <t>10일</t>
   </si>
   <si>
-    <t>456.3</t>
-  </si>
-  <si>
-    <t>4866.1</t>
+    <t>460.3</t>
+  </si>
+  <si>
+    <t>4870.1</t>
   </si>
   <si>
     <t>4.6</t>
@@ -179,10 +179,22 @@
     <t>11일</t>
   </si>
   <si>
+    <t>471.0</t>
+  </si>
+  <si>
+    <t>5341.1</t>
+  </si>
+  <si>
+    <t>4.7</t>
+  </si>
+  <si>
+    <t>53.4</t>
+  </si>
+  <si>
+    <t>12일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>12일</t>
   </si>
   <si>
     <t>13일</t>
@@ -753,13 +765,13 @@
         <v>55</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -767,19 +779,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -787,19 +799,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -807,19 +819,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -827,19 +839,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -847,19 +859,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -867,19 +879,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -887,19 +899,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -907,19 +919,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -927,19 +939,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -947,19 +959,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -967,19 +979,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -987,19 +999,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1007,19 +1019,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1027,19 +1039,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1047,19 +1059,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1067,19 +1079,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1087,19 +1099,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1107,19 +1119,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1127,19 +1139,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1147,19 +1159,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-08-01.xlsx
+++ b/past_data/site_8023/2026-08-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="83">
   <si>
     <t>No.</t>
   </si>
@@ -35,7 +35,7 @@
     <t>평균</t>
   </si>
   <si>
-    <t>485.6</t>
+    <t>491.8</t>
   </si>
   <si>
     <t>-</t>
@@ -179,25 +179,34 @@
     <t>11일</t>
   </si>
   <si>
-    <t>471.0</t>
-  </si>
-  <si>
-    <t>5341.1</t>
-  </si>
-  <si>
-    <t>4.7</t>
-  </si>
-  <si>
-    <t>53.4</t>
+    <t>477.7</t>
+  </si>
+  <si>
+    <t>5347.8</t>
+  </si>
+  <si>
+    <t>53.5</t>
   </si>
   <si>
     <t>12일</t>
   </si>
   <si>
+    <t>554.1</t>
+  </si>
+  <si>
+    <t>5901.9</t>
+  </si>
+  <si>
+    <t>5.5</t>
+  </si>
+  <si>
+    <t>59.0</t>
+  </si>
+  <si>
+    <t>13일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>13일</t>
   </si>
   <si>
     <t>14일</t>
@@ -768,10 +777,10 @@
         <v>56</v>
       </c>
       <c r="E13" t="s" s="33">
+        <v>16</v>
+      </c>
+      <c r="F13" t="s" s="34">
         <v>57</v>
-      </c>
-      <c r="F13" t="s" s="34">
-        <v>58</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -779,19 +788,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
+        <v>58</v>
+      </c>
+      <c r="C14" t="s" s="36">
         <v>59</v>
-      </c>
-      <c r="C14" t="s" s="36">
-        <v>60</v>
       </c>
       <c r="D14" t="s" s="37">
         <v>60</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -799,19 +808,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -819,19 +828,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -839,19 +848,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -859,19 +868,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -879,19 +888,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -899,19 +908,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -919,19 +928,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -939,19 +948,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -959,19 +968,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -979,19 +988,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -999,19 +1008,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1019,19 +1028,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1039,19 +1048,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1059,19 +1068,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1079,19 +1088,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1099,19 +1108,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1119,19 +1128,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1139,19 +1148,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1159,19 +1168,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-08-01.xlsx
+++ b/past_data/site_8023/2026-08-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="87">
   <si>
     <t>No.</t>
   </si>
@@ -35,78 +35,78 @@
     <t>평균</t>
   </si>
   <si>
-    <t>491.8</t>
+    <t>482.1</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
+    <t>4.8</t>
+  </si>
+  <si>
+    <t>01일</t>
+  </si>
+  <si>
+    <t>453.6</t>
+  </si>
+  <si>
+    <t>4.5</t>
+  </si>
+  <si>
+    <t>02일</t>
+  </si>
+  <si>
+    <t>475.8</t>
+  </si>
+  <si>
+    <t>929.4</t>
+  </si>
+  <si>
+    <t>9.3</t>
+  </si>
+  <si>
+    <t>03일</t>
+  </si>
+  <si>
+    <t>515.6</t>
+  </si>
+  <si>
+    <t>1445.0</t>
+  </si>
+  <si>
+    <t>5.2</t>
+  </si>
+  <si>
+    <t>14.5</t>
+  </si>
+  <si>
+    <t>04일</t>
+  </si>
+  <si>
+    <t>537.3</t>
+  </si>
+  <si>
+    <t>1982.3</t>
+  </si>
+  <si>
+    <t>5.4</t>
+  </si>
+  <si>
+    <t>19.8</t>
+  </si>
+  <si>
+    <t>05일</t>
+  </si>
+  <si>
+    <t>489.8</t>
+  </si>
+  <si>
+    <t>2472.1</t>
+  </si>
+  <si>
     <t>4.9</t>
   </si>
   <si>
-    <t>01일</t>
-  </si>
-  <si>
-    <t>453.6</t>
-  </si>
-  <si>
-    <t>4.5</t>
-  </si>
-  <si>
-    <t>02일</t>
-  </si>
-  <si>
-    <t>475.8</t>
-  </si>
-  <si>
-    <t>929.4</t>
-  </si>
-  <si>
-    <t>4.8</t>
-  </si>
-  <si>
-    <t>9.3</t>
-  </si>
-  <si>
-    <t>03일</t>
-  </si>
-  <si>
-    <t>515.6</t>
-  </si>
-  <si>
-    <t>1445.0</t>
-  </si>
-  <si>
-    <t>5.2</t>
-  </si>
-  <si>
-    <t>14.5</t>
-  </si>
-  <si>
-    <t>04일</t>
-  </si>
-  <si>
-    <t>537.3</t>
-  </si>
-  <si>
-    <t>1982.3</t>
-  </si>
-  <si>
-    <t>5.4</t>
-  </si>
-  <si>
-    <t>19.8</t>
-  </si>
-  <si>
-    <t>05일</t>
-  </si>
-  <si>
-    <t>489.8</t>
-  </si>
-  <si>
-    <t>2472.1</t>
-  </si>
-  <si>
     <t>24.7</t>
   </si>
   <si>
@@ -191,25 +191,37 @@
     <t>12일</t>
   </si>
   <si>
-    <t>554.1</t>
-  </si>
-  <si>
-    <t>5901.9</t>
-  </si>
-  <si>
-    <t>5.5</t>
-  </si>
-  <si>
-    <t>59.0</t>
+    <t>558.0</t>
+  </si>
+  <si>
+    <t>5905.8</t>
+  </si>
+  <si>
+    <t>5.6</t>
+  </si>
+  <si>
+    <t>59.1</t>
   </si>
   <si>
     <t>13일</t>
   </si>
   <si>
+    <t>361.1</t>
+  </si>
+  <si>
+    <t>6266.9</t>
+  </si>
+  <si>
+    <t>3.6</t>
+  </si>
+  <si>
+    <t>62.7</t>
+  </si>
+  <si>
+    <t>14일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>14일</t>
   </si>
   <si>
     <t>15일</t>
@@ -597,10 +609,10 @@
         <v>15</v>
       </c>
       <c r="E4" t="s" s="38">
+        <v>9</v>
+      </c>
+      <c r="F4" t="s" s="39">
         <v>16</v>
-      </c>
-      <c r="F4" t="s" s="39">
-        <v>17</v>
       </c>
     </row>
     <row r="5" ht="17.25" customHeight="1">
@@ -608,19 +620,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s" s="30">
+        <v>17</v>
+      </c>
+      <c r="C5" t="s" s="31">
         <v>18</v>
       </c>
-      <c r="C5" t="s" s="31">
+      <c r="D5" t="s" s="32">
         <v>19</v>
       </c>
-      <c r="D5" t="s" s="32">
+      <c r="E5" t="s" s="33">
         <v>20</v>
       </c>
-      <c r="E5" t="s" s="33">
+      <c r="F5" t="s" s="34">
         <v>21</v>
-      </c>
-      <c r="F5" t="s" s="34">
-        <v>22</v>
       </c>
     </row>
     <row r="6" ht="17.25" customHeight="1">
@@ -628,19 +640,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s" s="35">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s" s="36">
         <v>23</v>
       </c>
-      <c r="C6" t="s" s="36">
+      <c r="D6" t="s" s="37">
         <v>24</v>
       </c>
-      <c r="D6" t="s" s="37">
+      <c r="E6" t="s" s="38">
         <v>25</v>
       </c>
-      <c r="E6" t="s" s="38">
+      <c r="F6" t="s" s="39">
         <v>26</v>
-      </c>
-      <c r="F6" t="s" s="39">
-        <v>27</v>
       </c>
     </row>
     <row r="7" ht="17.25" customHeight="1">
@@ -648,16 +660,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="s" s="30">
+        <v>27</v>
+      </c>
+      <c r="C7" t="s" s="31">
         <v>28</v>
       </c>
-      <c r="C7" t="s" s="31">
+      <c r="D7" t="s" s="32">
         <v>29</v>
       </c>
-      <c r="D7" t="s" s="32">
+      <c r="E7" t="s" s="33">
         <v>30</v>
-      </c>
-      <c r="E7" t="s" s="33">
-        <v>9</v>
       </c>
       <c r="F7" t="s" s="34">
         <v>31</v>
@@ -677,7 +689,7 @@
         <v>34</v>
       </c>
       <c r="E8" t="s" s="38">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F8" t="s" s="39">
         <v>35</v>
@@ -697,7 +709,7 @@
         <v>38</v>
       </c>
       <c r="E9" t="s" s="33">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F9" t="s" s="34">
         <v>39</v>
@@ -717,7 +729,7 @@
         <v>42</v>
       </c>
       <c r="E10" t="s" s="38">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="F10" t="s" s="39">
         <v>43</v>
@@ -777,7 +789,7 @@
         <v>56</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="F13" t="s" s="34">
         <v>57</v>
@@ -814,13 +826,13 @@
         <v>64</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -828,19 +840,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>64</v>
+        <v>69</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -848,19 +860,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>64</v>
+        <v>69</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -868,19 +880,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>64</v>
+        <v>69</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -888,19 +900,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>64</v>
+        <v>69</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -908,19 +920,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>64</v>
+        <v>69</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -928,19 +940,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>64</v>
+        <v>69</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -948,19 +960,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>64</v>
+        <v>69</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -968,19 +980,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>64</v>
+        <v>69</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -988,19 +1000,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>64</v>
+        <v>69</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1008,19 +1020,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>64</v>
+        <v>69</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1028,19 +1040,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>64</v>
+        <v>69</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1048,19 +1060,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>64</v>
+        <v>69</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1068,19 +1080,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>64</v>
+        <v>69</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1088,19 +1100,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>64</v>
+        <v>69</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1108,19 +1120,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>64</v>
+        <v>69</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1128,19 +1140,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>64</v>
+        <v>69</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1148,19 +1160,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>64</v>
+        <v>69</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1168,19 +1180,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>64</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-08-01.xlsx
+++ b/past_data/site_8023/2026-08-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="92">
   <si>
     <t>No.</t>
   </si>
@@ -35,33 +35,36 @@
     <t>평균</t>
   </si>
   <si>
-    <t>482.1</t>
+    <t>471.4</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
+    <t>4.7</t>
+  </si>
+  <si>
+    <t>01일</t>
+  </si>
+  <si>
+    <t>453.6</t>
+  </si>
+  <si>
+    <t>4.5</t>
+  </si>
+  <si>
+    <t>02일</t>
+  </si>
+  <si>
+    <t>475.8</t>
+  </si>
+  <si>
+    <t>929.4</t>
+  </si>
+  <si>
     <t>4.8</t>
   </si>
   <si>
-    <t>01일</t>
-  </si>
-  <si>
-    <t>453.6</t>
-  </si>
-  <si>
-    <t>4.5</t>
-  </si>
-  <si>
-    <t>02일</t>
-  </si>
-  <si>
-    <t>475.8</t>
-  </si>
-  <si>
-    <t>929.4</t>
-  </si>
-  <si>
     <t>9.3</t>
   </si>
   <si>
@@ -206,13 +209,13 @@
     <t>13일</t>
   </si>
   <si>
-    <t>361.1</t>
-  </si>
-  <si>
-    <t>6266.9</t>
-  </si>
-  <si>
-    <t>3.6</t>
+    <t>365.1</t>
+  </si>
+  <si>
+    <t>6270.9</t>
+  </si>
+  <si>
+    <t>3.7</t>
   </si>
   <si>
     <t>62.7</t>
@@ -221,10 +224,22 @@
     <t>14일</t>
   </si>
   <si>
+    <t>329.1</t>
+  </si>
+  <si>
+    <t>6600.0</t>
+  </si>
+  <si>
+    <t>3.3</t>
+  </si>
+  <si>
+    <t>66.0</t>
+  </si>
+  <si>
+    <t>15일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>15일</t>
   </si>
   <si>
     <t>16일</t>
@@ -609,10 +624,10 @@
         <v>15</v>
       </c>
       <c r="E4" t="s" s="38">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="F4" t="s" s="39">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" ht="17.25" customHeight="1">
@@ -620,19 +635,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s" s="30">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s" s="31">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D5" t="s" s="32">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E5" t="s" s="33">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F5" t="s" s="34">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" ht="17.25" customHeight="1">
@@ -640,19 +655,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s" s="35">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s" s="36">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D6" t="s" s="37">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E6" t="s" s="38">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F6" t="s" s="39">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" ht="17.25" customHeight="1">
@@ -660,19 +675,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s" s="30">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C7" t="s" s="31">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D7" t="s" s="32">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E7" t="s" s="33">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F7" t="s" s="34">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" ht="17.25" customHeight="1">
@@ -680,19 +695,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s" s="35">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C8" t="s" s="36">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s" s="37">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E8" t="s" s="38">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F8" t="s" s="39">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" ht="17.25" customHeight="1">
@@ -700,19 +715,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s" s="30">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C9" t="s" s="31">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D9" t="s" s="32">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E9" t="s" s="33">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F9" t="s" s="34">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1">
@@ -720,19 +735,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s" s="35">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C10" t="s" s="36">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D10" t="s" s="37">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E10" t="s" s="38">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="F10" t="s" s="39">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1">
@@ -740,19 +755,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s" s="30">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C11" t="s" s="31">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D11" t="s" s="32">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E11" t="s" s="33">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F11" t="s" s="34">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -760,19 +775,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C12" t="s" s="36">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D12" t="s" s="37">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E12" t="s" s="38">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F12" t="s" s="39">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -780,19 +795,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C13" t="s" s="31">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -800,19 +815,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -820,19 +835,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -840,19 +855,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -860,19 +875,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>69</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -880,19 +895,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>69</v>
+        <v>75</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -900,19 +915,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>69</v>
+        <v>75</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -920,19 +935,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>69</v>
+        <v>75</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -940,19 +955,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>69</v>
+        <v>75</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -960,19 +975,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>69</v>
+        <v>75</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -980,19 +995,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>69</v>
+        <v>75</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -1000,19 +1015,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>69</v>
+        <v>75</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1020,19 +1035,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>69</v>
+        <v>75</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1040,19 +1055,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>69</v>
+        <v>75</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1060,19 +1075,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>69</v>
+        <v>75</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1080,19 +1095,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>69</v>
+        <v>75</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1100,19 +1115,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>69</v>
+        <v>75</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1120,19 +1135,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>69</v>
+        <v>75</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1140,19 +1155,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>69</v>
+        <v>75</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1160,19 +1175,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>69</v>
+        <v>75</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1180,19 +1195,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>69</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-08-01.xlsx
+++ b/past_data/site_8023/2026-08-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="95">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>471.4</t>
+    <t>453.3</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>4.7</t>
+    <t>4.5</t>
   </si>
   <si>
     <t>01일</t>
@@ -50,9 +50,6 @@
     <t>453.6</t>
   </si>
   <si>
-    <t>4.5</t>
-  </si>
-  <si>
     <t>02일</t>
   </si>
   <si>
@@ -224,10 +221,10 @@
     <t>14일</t>
   </si>
   <si>
-    <t>329.1</t>
-  </si>
-  <si>
-    <t>6600.0</t>
+    <t>332.3</t>
+  </si>
+  <si>
+    <t>6603.2</t>
   </si>
   <si>
     <t>3.3</t>
@@ -239,10 +236,22 @@
     <t>15일</t>
   </si>
   <si>
+    <t>196.6</t>
+  </si>
+  <si>
+    <t>6799.8</t>
+  </si>
+  <si>
+    <t>2.0</t>
+  </si>
+  <si>
+    <t>68.0</t>
+  </si>
+  <si>
+    <t>16일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>16일</t>
   </si>
   <si>
     <t>17일</t>
@@ -604,10 +613,10 @@
         <v>11</v>
       </c>
       <c r="E3" t="s" s="33">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s" s="34">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" ht="17.25" customHeight="1">
@@ -615,19 +624,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s" s="35">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s" s="36">
         <v>13</v>
       </c>
-      <c r="C4" t="s" s="36">
+      <c r="D4" t="s" s="37">
         <v>14</v>
       </c>
-      <c r="D4" t="s" s="37">
+      <c r="E4" t="s" s="38">
         <v>15</v>
       </c>
-      <c r="E4" t="s" s="38">
+      <c r="F4" t="s" s="39">
         <v>16</v>
-      </c>
-      <c r="F4" t="s" s="39">
-        <v>17</v>
       </c>
     </row>
     <row r="5" ht="17.25" customHeight="1">
@@ -635,19 +644,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s" s="30">
+        <v>17</v>
+      </c>
+      <c r="C5" t="s" s="31">
         <v>18</v>
       </c>
-      <c r="C5" t="s" s="31">
+      <c r="D5" t="s" s="32">
         <v>19</v>
       </c>
-      <c r="D5" t="s" s="32">
+      <c r="E5" t="s" s="33">
         <v>20</v>
       </c>
-      <c r="E5" t="s" s="33">
+      <c r="F5" t="s" s="34">
         <v>21</v>
-      </c>
-      <c r="F5" t="s" s="34">
-        <v>22</v>
       </c>
     </row>
     <row r="6" ht="17.25" customHeight="1">
@@ -655,19 +664,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s" s="35">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s" s="36">
         <v>23</v>
       </c>
-      <c r="C6" t="s" s="36">
+      <c r="D6" t="s" s="37">
         <v>24</v>
       </c>
-      <c r="D6" t="s" s="37">
+      <c r="E6" t="s" s="38">
         <v>25</v>
       </c>
-      <c r="E6" t="s" s="38">
+      <c r="F6" t="s" s="39">
         <v>26</v>
-      </c>
-      <c r="F6" t="s" s="39">
-        <v>27</v>
       </c>
     </row>
     <row r="7" ht="17.25" customHeight="1">
@@ -675,19 +684,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s" s="30">
+        <v>27</v>
+      </c>
+      <c r="C7" t="s" s="31">
         <v>28</v>
       </c>
-      <c r="C7" t="s" s="31">
+      <c r="D7" t="s" s="32">
         <v>29</v>
       </c>
-      <c r="D7" t="s" s="32">
+      <c r="E7" t="s" s="33">
         <v>30</v>
       </c>
-      <c r="E7" t="s" s="33">
+      <c r="F7" t="s" s="34">
         <v>31</v>
-      </c>
-      <c r="F7" t="s" s="34">
-        <v>32</v>
       </c>
     </row>
     <row r="8" ht="17.25" customHeight="1">
@@ -695,19 +704,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s" s="35">
+        <v>32</v>
+      </c>
+      <c r="C8" t="s" s="36">
         <v>33</v>
       </c>
-      <c r="C8" t="s" s="36">
+      <c r="D8" t="s" s="37">
         <v>34</v>
       </c>
-      <c r="D8" t="s" s="37">
+      <c r="E8" t="s" s="38">
+        <v>25</v>
+      </c>
+      <c r="F8" t="s" s="39">
         <v>35</v>
-      </c>
-      <c r="E8" t="s" s="38">
-        <v>26</v>
-      </c>
-      <c r="F8" t="s" s="39">
-        <v>36</v>
       </c>
     </row>
     <row r="9" ht="17.25" customHeight="1">
@@ -715,19 +724,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s" s="30">
+        <v>36</v>
+      </c>
+      <c r="C9" t="s" s="31">
         <v>37</v>
       </c>
-      <c r="C9" t="s" s="31">
+      <c r="D9" t="s" s="32">
         <v>38</v>
       </c>
-      <c r="D9" t="s" s="32">
+      <c r="E9" t="s" s="33">
+        <v>20</v>
+      </c>
+      <c r="F9" t="s" s="34">
         <v>39</v>
-      </c>
-      <c r="E9" t="s" s="33">
-        <v>21</v>
-      </c>
-      <c r="F9" t="s" s="34">
-        <v>40</v>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1">
@@ -735,19 +744,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s" s="35">
+        <v>40</v>
+      </c>
+      <c r="C10" t="s" s="36">
         <v>41</v>
       </c>
-      <c r="C10" t="s" s="36">
+      <c r="D10" t="s" s="37">
         <v>42</v>
       </c>
-      <c r="D10" t="s" s="37">
+      <c r="E10" t="s" s="38">
+        <v>15</v>
+      </c>
+      <c r="F10" t="s" s="39">
         <v>43</v>
-      </c>
-      <c r="E10" t="s" s="38">
-        <v>16</v>
-      </c>
-      <c r="F10" t="s" s="39">
-        <v>44</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1">
@@ -755,19 +764,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s" s="30">
+        <v>44</v>
+      </c>
+      <c r="C11" t="s" s="31">
         <v>45</v>
       </c>
-      <c r="C11" t="s" s="31">
+      <c r="D11" t="s" s="32">
         <v>46</v>
       </c>
-      <c r="D11" t="s" s="32">
+      <c r="E11" t="s" s="33">
         <v>47</v>
       </c>
-      <c r="E11" t="s" s="33">
+      <c r="F11" t="s" s="34">
         <v>48</v>
-      </c>
-      <c r="F11" t="s" s="34">
-        <v>49</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -775,19 +784,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
+        <v>49</v>
+      </c>
+      <c r="C12" t="s" s="36">
         <v>50</v>
       </c>
-      <c r="C12" t="s" s="36">
+      <c r="D12" t="s" s="37">
         <v>51</v>
       </c>
-      <c r="D12" t="s" s="37">
+      <c r="E12" t="s" s="38">
         <v>52</v>
       </c>
-      <c r="E12" t="s" s="38">
+      <c r="F12" t="s" s="39">
         <v>53</v>
-      </c>
-      <c r="F12" t="s" s="39">
-        <v>54</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -795,19 +804,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
+        <v>54</v>
+      </c>
+      <c r="C13" t="s" s="31">
         <v>55</v>
       </c>
-      <c r="C13" t="s" s="31">
+      <c r="D13" t="s" s="32">
         <v>56</v>
       </c>
-      <c r="D13" t="s" s="32">
+      <c r="E13" t="s" s="33">
+        <v>15</v>
+      </c>
+      <c r="F13" t="s" s="34">
         <v>57</v>
-      </c>
-      <c r="E13" t="s" s="33">
-        <v>16</v>
-      </c>
-      <c r="F13" t="s" s="34">
-        <v>58</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -815,19 +824,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
+        <v>58</v>
+      </c>
+      <c r="C14" t="s" s="36">
         <v>59</v>
       </c>
-      <c r="C14" t="s" s="36">
+      <c r="D14" t="s" s="37">
         <v>60</v>
       </c>
-      <c r="D14" t="s" s="37">
+      <c r="E14" t="s" s="38">
         <v>61</v>
       </c>
-      <c r="E14" t="s" s="38">
+      <c r="F14" t="s" s="39">
         <v>62</v>
-      </c>
-      <c r="F14" t="s" s="39">
-        <v>63</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -835,19 +844,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
+        <v>63</v>
+      </c>
+      <c r="C15" t="s" s="31">
         <v>64</v>
       </c>
-      <c r="C15" t="s" s="31">
+      <c r="D15" t="s" s="32">
         <v>65</v>
       </c>
-      <c r="D15" t="s" s="32">
+      <c r="E15" t="s" s="33">
         <v>66</v>
       </c>
-      <c r="E15" t="s" s="33">
+      <c r="F15" t="s" s="34">
         <v>67</v>
-      </c>
-      <c r="F15" t="s" s="34">
-        <v>68</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -855,19 +864,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
+        <v>68</v>
+      </c>
+      <c r="C16" t="s" s="36">
         <v>69</v>
       </c>
-      <c r="C16" t="s" s="36">
+      <c r="D16" t="s" s="37">
         <v>70</v>
       </c>
-      <c r="D16" t="s" s="37">
+      <c r="E16" t="s" s="38">
         <v>71</v>
       </c>
-      <c r="E16" t="s" s="38">
+      <c r="F16" t="s" s="39">
         <v>72</v>
-      </c>
-      <c r="F16" t="s" s="39">
-        <v>73</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -875,19 +884,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
+        <v>73</v>
+      </c>
+      <c r="C17" t="s" s="31">
         <v>74</v>
-      </c>
-      <c r="C17" t="s" s="31">
-        <v>75</v>
       </c>
       <c r="D17" t="s" s="32">
         <v>75</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -895,19 +904,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -915,19 +924,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -935,19 +944,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -955,19 +964,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -975,19 +984,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -995,19 +1004,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -1015,19 +1024,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1035,19 +1044,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1055,19 +1064,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1075,19 +1084,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1095,19 +1104,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1115,19 +1124,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1135,19 +1144,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1155,19 +1164,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1175,19 +1184,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1195,19 +1204,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-08-01.xlsx
+++ b/past_data/site_8023/2026-08-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="100">
   <si>
     <t>No.</t>
   </si>
@@ -35,21 +35,24 @@
     <t>평균</t>
   </si>
   <si>
-    <t>453.3</t>
+    <t>433.8</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
+    <t>4.3</t>
+  </si>
+  <si>
+    <t>01일</t>
+  </si>
+  <si>
+    <t>453.6</t>
+  </si>
+  <si>
     <t>4.5</t>
   </si>
   <si>
-    <t>01일</t>
-  </si>
-  <si>
-    <t>453.6</t>
-  </si>
-  <si>
     <t>02일</t>
   </si>
   <si>
@@ -236,25 +239,37 @@
     <t>15일</t>
   </si>
   <si>
-    <t>196.6</t>
-  </si>
-  <si>
-    <t>6799.8</t>
-  </si>
-  <si>
-    <t>2.0</t>
-  </si>
-  <si>
-    <t>68.0</t>
+    <t>206.6</t>
+  </si>
+  <si>
+    <t>6809.8</t>
+  </si>
+  <si>
+    <t>2.1</t>
+  </si>
+  <si>
+    <t>68.1</t>
   </si>
   <si>
     <t>16일</t>
   </si>
   <si>
+    <t>131.1</t>
+  </si>
+  <si>
+    <t>6940.9</t>
+  </si>
+  <si>
+    <t>1.3</t>
+  </si>
+  <si>
+    <t>69.4</t>
+  </si>
+  <si>
+    <t>17일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>17일</t>
   </si>
   <si>
     <t>18일</t>
@@ -613,10 +628,10 @@
         <v>11</v>
       </c>
       <c r="E3" t="s" s="33">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F3" t="s" s="34">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" ht="17.25" customHeight="1">
@@ -624,19 +639,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s" s="35">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s" s="36">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D4" t="s" s="37">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E4" t="s" s="38">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F4" t="s" s="39">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" ht="17.25" customHeight="1">
@@ -644,19 +659,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s" s="30">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s" s="31">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D5" t="s" s="32">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E5" t="s" s="33">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F5" t="s" s="34">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" ht="17.25" customHeight="1">
@@ -664,19 +679,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s" s="35">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s" s="36">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D6" t="s" s="37">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E6" t="s" s="38">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F6" t="s" s="39">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" ht="17.25" customHeight="1">
@@ -684,19 +699,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s" s="30">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C7" t="s" s="31">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D7" t="s" s="32">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E7" t="s" s="33">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F7" t="s" s="34">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" ht="17.25" customHeight="1">
@@ -704,19 +719,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s" s="35">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C8" t="s" s="36">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s" s="37">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E8" t="s" s="38">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F8" t="s" s="39">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" ht="17.25" customHeight="1">
@@ -724,19 +739,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s" s="30">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C9" t="s" s="31">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D9" t="s" s="32">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E9" t="s" s="33">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F9" t="s" s="34">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1">
@@ -744,19 +759,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s" s="35">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C10" t="s" s="36">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D10" t="s" s="37">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E10" t="s" s="38">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F10" t="s" s="39">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1">
@@ -764,19 +779,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s" s="30">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C11" t="s" s="31">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D11" t="s" s="32">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E11" t="s" s="33">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F11" t="s" s="34">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -784,19 +799,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C12" t="s" s="36">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D12" t="s" s="37">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E12" t="s" s="38">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F12" t="s" s="39">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -804,19 +819,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C13" t="s" s="31">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -824,19 +839,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -844,19 +859,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -864,19 +879,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -884,19 +899,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -904,19 +919,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -924,19 +939,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>79</v>
+        <v>85</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -944,19 +959,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>79</v>
+        <v>85</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -964,19 +979,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>79</v>
+        <v>85</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -984,19 +999,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>79</v>
+        <v>85</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -1004,19 +1019,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>79</v>
+        <v>85</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -1024,19 +1039,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>79</v>
+        <v>85</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1044,19 +1059,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>79</v>
+        <v>85</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1064,19 +1079,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>79</v>
+        <v>85</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1084,19 +1099,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>79</v>
+        <v>85</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1104,19 +1119,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>79</v>
+        <v>85</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1124,19 +1139,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>79</v>
+        <v>85</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1144,19 +1159,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>79</v>
+        <v>85</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1164,19 +1179,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>79</v>
+        <v>85</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1184,19 +1199,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>79</v>
+        <v>85</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1204,19 +1219,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>79</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-08-01.xlsx
+++ b/past_data/site_8023/2026-08-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="104">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>433.8</t>
+    <t>418.2</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>4.3</t>
+    <t>4.2</t>
   </si>
   <si>
     <t>01일</t>
@@ -254,25 +254,37 @@
     <t>16일</t>
   </si>
   <si>
-    <t>131.1</t>
-  </si>
-  <si>
-    <t>6940.9</t>
-  </si>
-  <si>
-    <t>1.3</t>
-  </si>
-  <si>
-    <t>69.4</t>
+    <t>145.1</t>
+  </si>
+  <si>
+    <t>6954.9</t>
+  </si>
+  <si>
+    <t>1.5</t>
+  </si>
+  <si>
+    <t>69.5</t>
   </si>
   <si>
     <t>17일</t>
   </si>
   <si>
+    <t>155.3</t>
+  </si>
+  <si>
+    <t>7110.2</t>
+  </si>
+  <si>
+    <t>1.6</t>
+  </si>
+  <si>
+    <t>71.1</t>
+  </si>
+  <si>
+    <t>18일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>18일</t>
   </si>
   <si>
     <t>19일</t>
@@ -945,13 +957,13 @@
         <v>85</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -959,19 +971,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -979,19 +991,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -999,19 +1011,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -1019,19 +1031,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -1039,19 +1051,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1059,19 +1071,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1079,19 +1091,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1099,19 +1111,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1119,19 +1131,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1139,19 +1151,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1159,19 +1171,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1179,19 +1191,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1199,19 +1211,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1219,19 +1231,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-08-01.xlsx
+++ b/past_data/site_8023/2026-08-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="108">
   <si>
     <t>No.</t>
   </si>
@@ -35,7 +35,7 @@
     <t>평균</t>
   </si>
   <si>
-    <t>418.2</t>
+    <t>423.2</t>
   </si>
   <si>
     <t>-</t>
@@ -269,10 +269,10 @@
     <t>17일</t>
   </si>
   <si>
-    <t>155.3</t>
-  </si>
-  <si>
-    <t>7110.2</t>
+    <t>157.5</t>
+  </si>
+  <si>
+    <t>7112.4</t>
   </si>
   <si>
     <t>1.6</t>
@@ -284,10 +284,22 @@
     <t>18일</t>
   </si>
   <si>
+    <t>504.7</t>
+  </si>
+  <si>
+    <t>7617.1</t>
+  </si>
+  <si>
+    <t>5.0</t>
+  </si>
+  <si>
+    <t>76.2</t>
+  </si>
+  <si>
+    <t>19일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>19일</t>
   </si>
   <si>
     <t>20일</t>
@@ -977,13 +989,13 @@
         <v>90</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>90</v>
+        <v>93</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -991,19 +1003,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -1011,19 +1023,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -1031,19 +1043,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -1051,19 +1063,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1071,19 +1083,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1091,19 +1103,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1111,19 +1123,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1131,19 +1143,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1151,19 +1163,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1171,19 +1183,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1191,19 +1203,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1211,19 +1223,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1231,19 +1243,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-08-01.xlsx
+++ b/past_data/site_8023/2026-08-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="115">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>423.2</t>
+    <t>408.4</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>4.2</t>
+    <t>4.1</t>
   </si>
   <si>
     <t>01일</t>
@@ -284,28 +284,49 @@
     <t>18일</t>
   </si>
   <si>
-    <t>504.7</t>
-  </si>
-  <si>
-    <t>7617.1</t>
-  </si>
-  <si>
-    <t>5.0</t>
-  </si>
-  <si>
-    <t>76.2</t>
+    <t>516.4</t>
+  </si>
+  <si>
+    <t>7628.8</t>
+  </si>
+  <si>
+    <t>76.3</t>
   </si>
   <si>
     <t>19일</t>
   </si>
   <si>
+    <t>363.0</t>
+  </si>
+  <si>
+    <t>7991.8</t>
+  </si>
+  <si>
+    <t>3.6</t>
+  </si>
+  <si>
+    <t>79.9</t>
+  </si>
+  <si>
+    <t>20일</t>
+  </si>
+  <si>
+    <t>176.6</t>
+  </si>
+  <si>
+    <t>8168.4</t>
+  </si>
+  <si>
+    <t>1.8</t>
+  </si>
+  <si>
+    <t>81.7</t>
+  </si>
+  <si>
+    <t>21일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>20일</t>
-  </si>
-  <si>
-    <t>21일</t>
   </si>
   <si>
     <t>22일</t>
@@ -992,10 +1013,10 @@
         <v>91</v>
       </c>
       <c r="E20" t="s" s="38">
+        <v>21</v>
+      </c>
+      <c r="F20" t="s" s="39">
         <v>92</v>
-      </c>
-      <c r="F20" t="s" s="39">
-        <v>93</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -1003,19 +1024,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
+        <v>93</v>
+      </c>
+      <c r="C21" t="s" s="31">
         <v>94</v>
-      </c>
-      <c r="C21" t="s" s="31">
-        <v>95</v>
       </c>
       <c r="D21" t="s" s="32">
         <v>95</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -1023,19 +1044,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>95</v>
+        <v>102</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -1043,19 +1064,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>95</v>
+        <v>104</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -1063,19 +1084,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>95</v>
+        <v>104</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1083,19 +1104,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>95</v>
+        <v>104</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1103,19 +1124,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>95</v>
+        <v>104</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1123,19 +1144,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>95</v>
+        <v>104</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1143,19 +1164,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>95</v>
+        <v>104</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1163,19 +1184,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>95</v>
+        <v>104</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1183,19 +1204,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>95</v>
+        <v>104</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1203,19 +1224,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>95</v>
+        <v>104</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1223,19 +1244,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>95</v>
+        <v>104</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1243,19 +1264,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>95</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-08-01.xlsx
+++ b/past_data/site_8023/2026-08-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="118">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>408.4</t>
+    <t>394.7</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>4.1</t>
+    <t>3.9</t>
   </si>
   <si>
     <t>01일</t>
@@ -158,9 +158,6 @@
     <t>4409.8</t>
   </si>
   <si>
-    <t>3.9</t>
-  </si>
-  <si>
     <t>44.1</t>
   </si>
   <si>
@@ -311,10 +308,10 @@
     <t>20일</t>
   </si>
   <si>
-    <t>176.6</t>
-  </si>
-  <si>
-    <t>8168.4</t>
+    <t>182.7</t>
+  </si>
+  <si>
+    <t>8174.5</t>
   </si>
   <si>
     <t>1.8</t>
@@ -326,10 +323,22 @@
     <t>21일</t>
   </si>
   <si>
+    <t>114.2</t>
+  </si>
+  <si>
+    <t>8288.7</t>
+  </si>
+  <si>
+    <t>1.1</t>
+  </si>
+  <si>
+    <t>82.9</t>
+  </si>
+  <si>
+    <t>22일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>22일</t>
   </si>
   <si>
     <t>23일</t>
@@ -833,10 +842,10 @@
         <v>47</v>
       </c>
       <c r="E11" t="s" s="33">
+        <v>9</v>
+      </c>
+      <c r="F11" t="s" s="34">
         <v>48</v>
-      </c>
-      <c r="F11" t="s" s="34">
-        <v>49</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -844,19 +853,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
+        <v>49</v>
+      </c>
+      <c r="C12" t="s" s="36">
         <v>50</v>
       </c>
-      <c r="C12" t="s" s="36">
+      <c r="D12" t="s" s="37">
         <v>51</v>
       </c>
-      <c r="D12" t="s" s="37">
+      <c r="E12" t="s" s="38">
         <v>52</v>
       </c>
-      <c r="E12" t="s" s="38">
+      <c r="F12" t="s" s="39">
         <v>53</v>
-      </c>
-      <c r="F12" t="s" s="39">
-        <v>54</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -864,19 +873,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
+        <v>54</v>
+      </c>
+      <c r="C13" t="s" s="31">
         <v>55</v>
       </c>
-      <c r="C13" t="s" s="31">
+      <c r="D13" t="s" s="32">
         <v>56</v>
-      </c>
-      <c r="D13" t="s" s="32">
-        <v>57</v>
       </c>
       <c r="E13" t="s" s="33">
         <v>16</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -884,19 +893,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
+        <v>58</v>
+      </c>
+      <c r="C14" t="s" s="36">
         <v>59</v>
       </c>
-      <c r="C14" t="s" s="36">
+      <c r="D14" t="s" s="37">
         <v>60</v>
       </c>
-      <c r="D14" t="s" s="37">
+      <c r="E14" t="s" s="38">
         <v>61</v>
       </c>
-      <c r="E14" t="s" s="38">
+      <c r="F14" t="s" s="39">
         <v>62</v>
-      </c>
-      <c r="F14" t="s" s="39">
-        <v>63</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -904,19 +913,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
+        <v>63</v>
+      </c>
+      <c r="C15" t="s" s="31">
         <v>64</v>
       </c>
-      <c r="C15" t="s" s="31">
+      <c r="D15" t="s" s="32">
         <v>65</v>
       </c>
-      <c r="D15" t="s" s="32">
+      <c r="E15" t="s" s="33">
         <v>66</v>
       </c>
-      <c r="E15" t="s" s="33">
+      <c r="F15" t="s" s="34">
         <v>67</v>
-      </c>
-      <c r="F15" t="s" s="34">
-        <v>68</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -924,19 +933,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
+        <v>68</v>
+      </c>
+      <c r="C16" t="s" s="36">
         <v>69</v>
       </c>
-      <c r="C16" t="s" s="36">
+      <c r="D16" t="s" s="37">
         <v>70</v>
       </c>
-      <c r="D16" t="s" s="37">
+      <c r="E16" t="s" s="38">
         <v>71</v>
       </c>
-      <c r="E16" t="s" s="38">
+      <c r="F16" t="s" s="39">
         <v>72</v>
-      </c>
-      <c r="F16" t="s" s="39">
-        <v>73</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -944,19 +953,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
+        <v>73</v>
+      </c>
+      <c r="C17" t="s" s="31">
         <v>74</v>
       </c>
-      <c r="C17" t="s" s="31">
+      <c r="D17" t="s" s="32">
         <v>75</v>
       </c>
-      <c r="D17" t="s" s="32">
+      <c r="E17" t="s" s="33">
         <v>76</v>
       </c>
-      <c r="E17" t="s" s="33">
+      <c r="F17" t="s" s="34">
         <v>77</v>
-      </c>
-      <c r="F17" t="s" s="34">
-        <v>78</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -964,19 +973,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
+        <v>78</v>
+      </c>
+      <c r="C18" t="s" s="36">
         <v>79</v>
       </c>
-      <c r="C18" t="s" s="36">
+      <c r="D18" t="s" s="37">
         <v>80</v>
       </c>
-      <c r="D18" t="s" s="37">
+      <c r="E18" t="s" s="38">
         <v>81</v>
       </c>
-      <c r="E18" t="s" s="38">
+      <c r="F18" t="s" s="39">
         <v>82</v>
-      </c>
-      <c r="F18" t="s" s="39">
-        <v>83</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -984,19 +993,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
+        <v>83</v>
+      </c>
+      <c r="C19" t="s" s="31">
         <v>84</v>
       </c>
-      <c r="C19" t="s" s="31">
+      <c r="D19" t="s" s="32">
         <v>85</v>
       </c>
-      <c r="D19" t="s" s="32">
+      <c r="E19" t="s" s="33">
         <v>86</v>
       </c>
-      <c r="E19" t="s" s="33">
+      <c r="F19" t="s" s="34">
         <v>87</v>
-      </c>
-      <c r="F19" t="s" s="34">
-        <v>88</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -1004,19 +1013,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
+        <v>88</v>
+      </c>
+      <c r="C20" t="s" s="36">
         <v>89</v>
       </c>
-      <c r="C20" t="s" s="36">
+      <c r="D20" t="s" s="37">
         <v>90</v>
-      </c>
-      <c r="D20" t="s" s="37">
-        <v>91</v>
       </c>
       <c r="E20" t="s" s="38">
         <v>21</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -1024,19 +1033,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
+        <v>92</v>
+      </c>
+      <c r="C21" t="s" s="31">
         <v>93</v>
       </c>
-      <c r="C21" t="s" s="31">
+      <c r="D21" t="s" s="32">
         <v>94</v>
       </c>
-      <c r="D21" t="s" s="32">
+      <c r="E21" t="s" s="33">
         <v>95</v>
       </c>
-      <c r="E21" t="s" s="33">
+      <c r="F21" t="s" s="34">
         <v>96</v>
-      </c>
-      <c r="F21" t="s" s="34">
-        <v>97</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -1044,19 +1053,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
+        <v>97</v>
+      </c>
+      <c r="C22" t="s" s="36">
         <v>98</v>
       </c>
-      <c r="C22" t="s" s="36">
+      <c r="D22" t="s" s="37">
         <v>99</v>
       </c>
-      <c r="D22" t="s" s="37">
+      <c r="E22" t="s" s="38">
         <v>100</v>
       </c>
-      <c r="E22" t="s" s="38">
+      <c r="F22" t="s" s="39">
         <v>101</v>
-      </c>
-      <c r="F22" t="s" s="39">
-        <v>102</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -1064,19 +1073,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
+        <v>102</v>
+      </c>
+      <c r="C23" t="s" s="31">
         <v>103</v>
-      </c>
-      <c r="C23" t="s" s="31">
-        <v>104</v>
       </c>
       <c r="D23" t="s" s="32">
         <v>104</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -1084,19 +1093,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>104</v>
+        <v>108</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1104,19 +1113,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>104</v>
+        <v>108</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1124,19 +1133,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>104</v>
+        <v>108</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1144,19 +1153,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>104</v>
+        <v>108</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1164,19 +1173,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>104</v>
+        <v>108</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1184,19 +1193,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>104</v>
+        <v>108</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1204,19 +1213,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>104</v>
+        <v>108</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1224,19 +1233,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>104</v>
+        <v>108</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1244,19 +1253,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>104</v>
+        <v>108</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1264,19 +1273,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>104</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-08-01.xlsx
+++ b/past_data/site_8023/2026-08-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="121">
   <si>
     <t>No.</t>
   </si>
@@ -35,7 +35,7 @@
     <t>평균</t>
   </si>
   <si>
-    <t>394.7</t>
+    <t>385.4</t>
   </si>
   <si>
     <t>-</t>
@@ -323,13 +323,13 @@
     <t>21일</t>
   </si>
   <si>
-    <t>114.2</t>
-  </si>
-  <si>
-    <t>8288.7</t>
-  </si>
-  <si>
-    <t>1.1</t>
+    <t>119.4</t>
+  </si>
+  <si>
+    <t>8293.9</t>
+  </si>
+  <si>
+    <t>1.2</t>
   </si>
   <si>
     <t>82.9</t>
@@ -338,10 +338,19 @@
     <t>22일</t>
   </si>
   <si>
+    <t>184.1</t>
+  </si>
+  <si>
+    <t>8478.0</t>
+  </si>
+  <si>
+    <t>84.8</t>
+  </si>
+  <si>
+    <t>23일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>23일</t>
   </si>
   <si>
     <t>24일</t>
@@ -1099,13 +1108,13 @@
         <v>108</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1113,19 +1122,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1133,19 +1142,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1153,19 +1162,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1173,19 +1182,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1193,19 +1202,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1213,19 +1222,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1233,19 +1242,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1253,19 +1262,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1273,19 +1282,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-08-01.xlsx
+++ b/past_data/site_8023/2026-08-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="126">
   <si>
     <t>No.</t>
   </si>
@@ -35,7 +35,7 @@
     <t>평균</t>
   </si>
   <si>
-    <t>385.4</t>
+    <t>390.5</t>
   </si>
   <si>
     <t>-</t>
@@ -338,10 +338,13 @@
     <t>22일</t>
   </si>
   <si>
-    <t>184.1</t>
-  </si>
-  <si>
-    <t>8478.0</t>
+    <t>185.8</t>
+  </si>
+  <si>
+    <t>8479.7</t>
+  </si>
+  <si>
+    <t>1.9</t>
   </si>
   <si>
     <t>84.8</t>
@@ -350,10 +353,22 @@
     <t>23일</t>
   </si>
   <si>
+    <t>502.0</t>
+  </si>
+  <si>
+    <t>8981.7</t>
+  </si>
+  <si>
+    <t>5.0</t>
+  </si>
+  <si>
+    <t>89.8</t>
+  </si>
+  <si>
+    <t>24일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>24일</t>
   </si>
   <si>
     <t>25일</t>
@@ -1111,10 +1126,10 @@
         <v>109</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1122,19 +1137,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1142,19 +1157,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>112</v>
+        <v>118</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1162,19 +1177,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>112</v>
+        <v>118</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1182,19 +1197,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>112</v>
+        <v>118</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1202,19 +1217,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>112</v>
+        <v>118</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1222,19 +1237,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>112</v>
+        <v>118</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1242,19 +1257,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>112</v>
+        <v>118</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1262,19 +1277,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>112</v>
+        <v>118</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1282,19 +1297,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>112</v>
+        <v>118</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-08-01.xlsx
+++ b/past_data/site_8023/2026-08-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="129">
   <si>
     <t>No.</t>
   </si>
@@ -35,7 +35,7 @@
     <t>평균</t>
   </si>
   <si>
-    <t>390.5</t>
+    <t>394.3</t>
   </si>
   <si>
     <t>-</t>
@@ -353,25 +353,34 @@
     <t>23일</t>
   </si>
   <si>
-    <t>502.0</t>
-  </si>
-  <si>
-    <t>8981.7</t>
-  </si>
-  <si>
-    <t>5.0</t>
-  </si>
-  <si>
-    <t>89.8</t>
+    <t>515.2</t>
+  </si>
+  <si>
+    <t>8994.9</t>
+  </si>
+  <si>
+    <t>89.9</t>
   </si>
   <si>
     <t>24일</t>
   </si>
   <si>
+    <t>468.0</t>
+  </si>
+  <si>
+    <t>9462.9</t>
+  </si>
+  <si>
+    <t>4.7</t>
+  </si>
+  <si>
+    <t>94.6</t>
+  </si>
+  <si>
+    <t>25일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>25일</t>
   </si>
   <si>
     <t>26일</t>
@@ -1146,10 +1155,10 @@
         <v>114</v>
       </c>
       <c r="E25" t="s" s="33">
+        <v>21</v>
+      </c>
+      <c r="F25" t="s" s="34">
         <v>115</v>
-      </c>
-      <c r="F25" t="s" s="34">
-        <v>116</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1157,19 +1166,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
+        <v>116</v>
+      </c>
+      <c r="C26" t="s" s="36">
         <v>117</v>
-      </c>
-      <c r="C26" t="s" s="36">
-        <v>118</v>
       </c>
       <c r="D26" t="s" s="37">
         <v>118</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1177,19 +1186,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>118</v>
+        <v>122</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1197,19 +1206,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>118</v>
+        <v>122</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1217,19 +1226,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>118</v>
+        <v>122</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1237,19 +1246,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>118</v>
+        <v>122</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1257,19 +1266,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>118</v>
+        <v>122</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1277,19 +1286,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>118</v>
+        <v>122</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1297,19 +1306,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>118</v>
+        <v>122</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-08-01.xlsx
+++ b/past_data/site_8023/2026-08-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="132">
   <si>
     <t>No.</t>
   </si>
@@ -35,7 +35,7 @@
     <t>평균</t>
   </si>
   <si>
-    <t>394.3</t>
+    <t>394.1</t>
   </si>
   <si>
     <t>-</t>
@@ -365,25 +365,34 @@
     <t>24일</t>
   </si>
   <si>
-    <t>468.0</t>
-  </si>
-  <si>
-    <t>9462.9</t>
-  </si>
-  <si>
-    <t>4.7</t>
-  </si>
-  <si>
-    <t>94.6</t>
+    <t>475.5</t>
+  </si>
+  <si>
+    <t>9470.4</t>
+  </si>
+  <si>
+    <t>94.7</t>
   </si>
   <si>
     <t>25일</t>
   </si>
   <si>
+    <t>382.0</t>
+  </si>
+  <si>
+    <t>9852.4</t>
+  </si>
+  <si>
+    <t>3.8</t>
+  </si>
+  <si>
+    <t>98.5</t>
+  </si>
+  <si>
+    <t>26일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>26일</t>
   </si>
   <si>
     <t>27일</t>
@@ -1175,10 +1184,10 @@
         <v>118</v>
       </c>
       <c r="E26" t="s" s="38">
+        <v>16</v>
+      </c>
+      <c r="F26" t="s" s="39">
         <v>119</v>
-      </c>
-      <c r="F26" t="s" s="39">
-        <v>120</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1186,19 +1195,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
+        <v>120</v>
+      </c>
+      <c r="C27" t="s" s="31">
         <v>121</v>
-      </c>
-      <c r="C27" t="s" s="31">
-        <v>122</v>
       </c>
       <c r="D27" t="s" s="32">
         <v>122</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1206,19 +1215,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1226,19 +1235,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1246,19 +1255,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1266,19 +1275,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1286,19 +1295,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1306,19 +1315,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-08-01.xlsx
+++ b/past_data/site_8023/2026-08-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="139">
   <si>
     <t>No.</t>
   </si>
@@ -35,7 +35,7 @@
     <t>평균</t>
   </si>
   <si>
-    <t>394.1</t>
+    <t>390.0</t>
   </si>
   <si>
     <t>-</t>
@@ -377,28 +377,49 @@
     <t>25일</t>
   </si>
   <si>
-    <t>382.0</t>
-  </si>
-  <si>
-    <t>9852.4</t>
-  </si>
-  <si>
-    <t>3.8</t>
-  </si>
-  <si>
-    <t>98.5</t>
+    <t>391.2</t>
+  </si>
+  <si>
+    <t>9861.6</t>
+  </si>
+  <si>
+    <t>98.6</t>
   </si>
   <si>
     <t>26일</t>
   </si>
   <si>
+    <t>318.2</t>
+  </si>
+  <si>
+    <t>10179.8</t>
+  </si>
+  <si>
+    <t>3.2</t>
+  </si>
+  <si>
+    <t>101.8</t>
+  </si>
+  <si>
+    <t>27일</t>
+  </si>
+  <si>
+    <t>351.2</t>
+  </si>
+  <si>
+    <t>10531.0</t>
+  </si>
+  <si>
+    <t>3.5</t>
+  </si>
+  <si>
+    <t>105.3</t>
+  </si>
+  <si>
+    <t>28일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>27일</t>
-  </si>
-  <si>
-    <t>28일</t>
   </si>
   <si>
     <t>29일</t>
@@ -1204,10 +1225,10 @@
         <v>122</v>
       </c>
       <c r="E27" t="s" s="33">
+        <v>9</v>
+      </c>
+      <c r="F27" t="s" s="34">
         <v>123</v>
-      </c>
-      <c r="F27" t="s" s="34">
-        <v>124</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1215,19 +1236,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
+        <v>124</v>
+      </c>
+      <c r="C28" t="s" s="36">
         <v>125</v>
-      </c>
-      <c r="C28" t="s" s="36">
-        <v>126</v>
       </c>
       <c r="D28" t="s" s="37">
         <v>126</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1235,19 +1256,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>126</v>
+        <v>133</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1255,19 +1276,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>126</v>
+        <v>135</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1275,19 +1296,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>126</v>
+        <v>135</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1295,19 +1316,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>126</v>
+        <v>135</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1315,19 +1336,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>126</v>
+        <v>135</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-08-01.xlsx
+++ b/past_data/site_8023/2026-08-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="144">
   <si>
     <t>No.</t>
   </si>
@@ -35,129 +35,132 @@
     <t>평균</t>
   </si>
   <si>
-    <t>390.0</t>
+    <t>379.6</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
+    <t>3.8</t>
+  </si>
+  <si>
+    <t>01일</t>
+  </si>
+  <si>
+    <t>453.6</t>
+  </si>
+  <si>
+    <t>4.5</t>
+  </si>
+  <si>
+    <t>02일</t>
+  </si>
+  <si>
+    <t>475.8</t>
+  </si>
+  <si>
+    <t>929.4</t>
+  </si>
+  <si>
+    <t>4.8</t>
+  </si>
+  <si>
+    <t>9.3</t>
+  </si>
+  <si>
+    <t>03일</t>
+  </si>
+  <si>
+    <t>515.6</t>
+  </si>
+  <si>
+    <t>1445.0</t>
+  </si>
+  <si>
+    <t>5.2</t>
+  </si>
+  <si>
+    <t>14.5</t>
+  </si>
+  <si>
+    <t>04일</t>
+  </si>
+  <si>
+    <t>537.3</t>
+  </si>
+  <si>
+    <t>1982.3</t>
+  </si>
+  <si>
+    <t>5.4</t>
+  </si>
+  <si>
+    <t>19.8</t>
+  </si>
+  <si>
+    <t>05일</t>
+  </si>
+  <si>
+    <t>489.8</t>
+  </si>
+  <si>
+    <t>2472.1</t>
+  </si>
+  <si>
+    <t>4.9</t>
+  </si>
+  <si>
+    <t>24.7</t>
+  </si>
+  <si>
+    <t>06일</t>
+  </si>
+  <si>
+    <t>540.1</t>
+  </si>
+  <si>
+    <t>3012.2</t>
+  </si>
+  <si>
+    <t>30.1</t>
+  </si>
+  <si>
+    <t>07일</t>
+  </si>
+  <si>
+    <t>523.4</t>
+  </si>
+  <si>
+    <t>3535.6</t>
+  </si>
+  <si>
+    <t>35.4</t>
+  </si>
+  <si>
+    <t>08일</t>
+  </si>
+  <si>
+    <t>482.2</t>
+  </si>
+  <si>
+    <t>4017.8</t>
+  </si>
+  <si>
+    <t>40.2</t>
+  </si>
+  <si>
+    <t>09일</t>
+  </si>
+  <si>
+    <t>392.0</t>
+  </si>
+  <si>
+    <t>4409.8</t>
+  </si>
+  <si>
     <t>3.9</t>
   </si>
   <si>
-    <t>01일</t>
-  </si>
-  <si>
-    <t>453.6</t>
-  </si>
-  <si>
-    <t>4.5</t>
-  </si>
-  <si>
-    <t>02일</t>
-  </si>
-  <si>
-    <t>475.8</t>
-  </si>
-  <si>
-    <t>929.4</t>
-  </si>
-  <si>
-    <t>4.8</t>
-  </si>
-  <si>
-    <t>9.3</t>
-  </si>
-  <si>
-    <t>03일</t>
-  </si>
-  <si>
-    <t>515.6</t>
-  </si>
-  <si>
-    <t>1445.0</t>
-  </si>
-  <si>
-    <t>5.2</t>
-  </si>
-  <si>
-    <t>14.5</t>
-  </si>
-  <si>
-    <t>04일</t>
-  </si>
-  <si>
-    <t>537.3</t>
-  </si>
-  <si>
-    <t>1982.3</t>
-  </si>
-  <si>
-    <t>5.4</t>
-  </si>
-  <si>
-    <t>19.8</t>
-  </si>
-  <si>
-    <t>05일</t>
-  </si>
-  <si>
-    <t>489.8</t>
-  </si>
-  <si>
-    <t>2472.1</t>
-  </si>
-  <si>
-    <t>4.9</t>
-  </si>
-  <si>
-    <t>24.7</t>
-  </si>
-  <si>
-    <t>06일</t>
-  </si>
-  <si>
-    <t>540.1</t>
-  </si>
-  <si>
-    <t>3012.2</t>
-  </si>
-  <si>
-    <t>30.1</t>
-  </si>
-  <si>
-    <t>07일</t>
-  </si>
-  <si>
-    <t>523.4</t>
-  </si>
-  <si>
-    <t>3535.6</t>
-  </si>
-  <si>
-    <t>35.4</t>
-  </si>
-  <si>
-    <t>08일</t>
-  </si>
-  <si>
-    <t>482.2</t>
-  </si>
-  <si>
-    <t>4017.8</t>
-  </si>
-  <si>
-    <t>40.2</t>
-  </si>
-  <si>
-    <t>09일</t>
-  </si>
-  <si>
-    <t>392.0</t>
-  </si>
-  <si>
-    <t>4409.8</t>
-  </si>
-  <si>
     <t>44.1</t>
   </si>
   <si>
@@ -419,10 +422,22 @@
     <t>28일</t>
   </si>
   <si>
+    <t>96.4</t>
+  </si>
+  <si>
+    <t>10627.4</t>
+  </si>
+  <si>
+    <t>1.0</t>
+  </si>
+  <si>
+    <t>106.3</t>
+  </si>
+  <si>
+    <t>29일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>29일</t>
   </si>
   <si>
     <t>30일</t>
@@ -905,10 +920,10 @@
         <v>47</v>
       </c>
       <c r="E11" t="s" s="33">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="F11" t="s" s="34">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -916,19 +931,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C12" t="s" s="36">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D12" t="s" s="37">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E12" t="s" s="38">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F12" t="s" s="39">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -936,19 +951,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C13" t="s" s="31">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E13" t="s" s="33">
         <v>16</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -956,19 +971,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -976,19 +991,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -996,19 +1011,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -1016,19 +1031,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -1036,19 +1051,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -1056,19 +1071,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -1076,19 +1091,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E20" t="s" s="38">
         <v>21</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -1096,19 +1111,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -1116,19 +1131,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -1136,19 +1151,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -1156,19 +1171,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1176,19 +1191,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E25" t="s" s="33">
         <v>21</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1196,19 +1211,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E26" t="s" s="38">
         <v>16</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1216,19 +1231,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1236,19 +1251,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1256,19 +1271,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1276,19 +1291,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>135</v>
+        <v>139</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1296,19 +1311,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>135</v>
+        <v>141</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1316,19 +1331,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>135</v>
+        <v>141</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1336,19 +1351,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>135</v>
+        <v>141</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-08-01.xlsx
+++ b/past_data/site_8023/2026-08-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="148">
   <si>
     <t>No.</t>
   </si>
@@ -35,7 +35,7 @@
     <t>평균</t>
   </si>
   <si>
-    <t>379.6</t>
+    <t>376.9</t>
   </si>
   <si>
     <t>-</t>
@@ -437,10 +437,22 @@
     <t>29일</t>
   </si>
   <si>
+    <t>301.6</t>
+  </si>
+  <si>
+    <t>10929.0</t>
+  </si>
+  <si>
+    <t>3.0</t>
+  </si>
+  <si>
+    <t>109.3</t>
+  </si>
+  <si>
+    <t>30일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>30일</t>
   </si>
   <si>
     <t>31일</t>
@@ -1317,13 +1329,13 @@
         <v>141</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1331,19 +1343,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>141</v>
+        <v>146</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1351,19 +1363,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>141</v>
+        <v>146</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-08-01.xlsx
+++ b/past_data/site_8023/2026-08-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="151">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>376.9</t>
+    <t>372.4</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>3.8</t>
+    <t>3.7</t>
   </si>
   <si>
     <t>01일</t>
@@ -215,9 +215,6 @@
     <t>6270.9</t>
   </si>
   <si>
-    <t>3.7</t>
-  </si>
-  <si>
     <t>62.7</t>
   </si>
   <si>
@@ -452,10 +449,22 @@
     <t>30일</t>
   </si>
   <si>
+    <t>241.6</t>
+  </si>
+  <si>
+    <t>11170.6</t>
+  </si>
+  <si>
+    <t>2.4</t>
+  </si>
+  <si>
+    <t>111.7</t>
+  </si>
+  <si>
+    <t>31일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>31일</t>
   </si>
 </sst>
 </file>
@@ -1012,10 +1021,10 @@
         <v>66</v>
       </c>
       <c r="E15" t="s" s="33">
+        <v>9</v>
+      </c>
+      <c r="F15" t="s" s="34">
         <v>67</v>
-      </c>
-      <c r="F15" t="s" s="34">
-        <v>68</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -1023,19 +1032,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
+        <v>68</v>
+      </c>
+      <c r="C16" t="s" s="36">
         <v>69</v>
       </c>
-      <c r="C16" t="s" s="36">
+      <c r="D16" t="s" s="37">
         <v>70</v>
       </c>
-      <c r="D16" t="s" s="37">
+      <c r="E16" t="s" s="38">
         <v>71</v>
       </c>
-      <c r="E16" t="s" s="38">
+      <c r="F16" t="s" s="39">
         <v>72</v>
-      </c>
-      <c r="F16" t="s" s="39">
-        <v>73</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -1043,19 +1052,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
+        <v>73</v>
+      </c>
+      <c r="C17" t="s" s="31">
         <v>74</v>
       </c>
-      <c r="C17" t="s" s="31">
+      <c r="D17" t="s" s="32">
         <v>75</v>
       </c>
-      <c r="D17" t="s" s="32">
+      <c r="E17" t="s" s="33">
         <v>76</v>
       </c>
-      <c r="E17" t="s" s="33">
+      <c r="F17" t="s" s="34">
         <v>77</v>
-      </c>
-      <c r="F17" t="s" s="34">
-        <v>78</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -1063,19 +1072,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
+        <v>78</v>
+      </c>
+      <c r="C18" t="s" s="36">
         <v>79</v>
       </c>
-      <c r="C18" t="s" s="36">
+      <c r="D18" t="s" s="37">
         <v>80</v>
       </c>
-      <c r="D18" t="s" s="37">
+      <c r="E18" t="s" s="38">
         <v>81</v>
       </c>
-      <c r="E18" t="s" s="38">
+      <c r="F18" t="s" s="39">
         <v>82</v>
-      </c>
-      <c r="F18" t="s" s="39">
-        <v>83</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -1083,19 +1092,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
+        <v>83</v>
+      </c>
+      <c r="C19" t="s" s="31">
         <v>84</v>
       </c>
-      <c r="C19" t="s" s="31">
+      <c r="D19" t="s" s="32">
         <v>85</v>
       </c>
-      <c r="D19" t="s" s="32">
+      <c r="E19" t="s" s="33">
         <v>86</v>
       </c>
-      <c r="E19" t="s" s="33">
+      <c r="F19" t="s" s="34">
         <v>87</v>
-      </c>
-      <c r="F19" t="s" s="34">
-        <v>88</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -1103,19 +1112,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
+        <v>88</v>
+      </c>
+      <c r="C20" t="s" s="36">
         <v>89</v>
       </c>
-      <c r="C20" t="s" s="36">
+      <c r="D20" t="s" s="37">
         <v>90</v>
-      </c>
-      <c r="D20" t="s" s="37">
-        <v>91</v>
       </c>
       <c r="E20" t="s" s="38">
         <v>21</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -1123,19 +1132,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
+        <v>92</v>
+      </c>
+      <c r="C21" t="s" s="31">
         <v>93</v>
       </c>
-      <c r="C21" t="s" s="31">
+      <c r="D21" t="s" s="32">
         <v>94</v>
       </c>
-      <c r="D21" t="s" s="32">
+      <c r="E21" t="s" s="33">
         <v>95</v>
       </c>
-      <c r="E21" t="s" s="33">
+      <c r="F21" t="s" s="34">
         <v>96</v>
-      </c>
-      <c r="F21" t="s" s="34">
-        <v>97</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -1143,19 +1152,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
+        <v>97</v>
+      </c>
+      <c r="C22" t="s" s="36">
         <v>98</v>
       </c>
-      <c r="C22" t="s" s="36">
+      <c r="D22" t="s" s="37">
         <v>99</v>
       </c>
-      <c r="D22" t="s" s="37">
+      <c r="E22" t="s" s="38">
         <v>100</v>
       </c>
-      <c r="E22" t="s" s="38">
+      <c r="F22" t="s" s="39">
         <v>101</v>
-      </c>
-      <c r="F22" t="s" s="39">
-        <v>102</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -1163,19 +1172,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
+        <v>102</v>
+      </c>
+      <c r="C23" t="s" s="31">
         <v>103</v>
       </c>
-      <c r="C23" t="s" s="31">
+      <c r="D23" t="s" s="32">
         <v>104</v>
       </c>
-      <c r="D23" t="s" s="32">
+      <c r="E23" t="s" s="33">
         <v>105</v>
       </c>
-      <c r="E23" t="s" s="33">
+      <c r="F23" t="s" s="34">
         <v>106</v>
-      </c>
-      <c r="F23" t="s" s="34">
-        <v>107</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -1183,19 +1192,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
+        <v>107</v>
+      </c>
+      <c r="C24" t="s" s="36">
         <v>108</v>
       </c>
-      <c r="C24" t="s" s="36">
+      <c r="D24" t="s" s="37">
         <v>109</v>
       </c>
-      <c r="D24" t="s" s="37">
+      <c r="E24" t="s" s="38">
         <v>110</v>
       </c>
-      <c r="E24" t="s" s="38">
+      <c r="F24" t="s" s="39">
         <v>111</v>
-      </c>
-      <c r="F24" t="s" s="39">
-        <v>112</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1203,19 +1212,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
+        <v>112</v>
+      </c>
+      <c r="C25" t="s" s="31">
         <v>113</v>
       </c>
-      <c r="C25" t="s" s="31">
+      <c r="D25" t="s" s="32">
         <v>114</v>
-      </c>
-      <c r="D25" t="s" s="32">
-        <v>115</v>
       </c>
       <c r="E25" t="s" s="33">
         <v>21</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1223,19 +1232,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
+        <v>116</v>
+      </c>
+      <c r="C26" t="s" s="36">
         <v>117</v>
       </c>
-      <c r="C26" t="s" s="36">
+      <c r="D26" t="s" s="37">
         <v>118</v>
-      </c>
-      <c r="D26" t="s" s="37">
-        <v>119</v>
       </c>
       <c r="E26" t="s" s="38">
         <v>16</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1243,19 +1252,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
+        <v>120</v>
+      </c>
+      <c r="C27" t="s" s="31">
         <v>121</v>
       </c>
-      <c r="C27" t="s" s="31">
+      <c r="D27" t="s" s="32">
         <v>122</v>
-      </c>
-      <c r="D27" t="s" s="32">
-        <v>123</v>
       </c>
       <c r="E27" t="s" s="33">
         <v>48</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1263,19 +1272,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
+        <v>124</v>
+      </c>
+      <c r="C28" t="s" s="36">
         <v>125</v>
       </c>
-      <c r="C28" t="s" s="36">
+      <c r="D28" t="s" s="37">
         <v>126</v>
       </c>
-      <c r="D28" t="s" s="37">
+      <c r="E28" t="s" s="38">
         <v>127</v>
       </c>
-      <c r="E28" t="s" s="38">
+      <c r="F28" t="s" s="39">
         <v>128</v>
-      </c>
-      <c r="F28" t="s" s="39">
-        <v>129</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1283,19 +1292,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
+        <v>129</v>
+      </c>
+      <c r="C29" t="s" s="31">
         <v>130</v>
       </c>
-      <c r="C29" t="s" s="31">
+      <c r="D29" t="s" s="32">
         <v>131</v>
       </c>
-      <c r="D29" t="s" s="32">
+      <c r="E29" t="s" s="33">
         <v>132</v>
       </c>
-      <c r="E29" t="s" s="33">
+      <c r="F29" t="s" s="34">
         <v>133</v>
-      </c>
-      <c r="F29" t="s" s="34">
-        <v>134</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1303,19 +1312,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
+        <v>134</v>
+      </c>
+      <c r="C30" t="s" s="36">
         <v>135</v>
       </c>
-      <c r="C30" t="s" s="36">
+      <c r="D30" t="s" s="37">
         <v>136</v>
       </c>
-      <c r="D30" t="s" s="37">
+      <c r="E30" t="s" s="38">
         <v>137</v>
       </c>
-      <c r="E30" t="s" s="38">
+      <c r="F30" t="s" s="39">
         <v>138</v>
-      </c>
-      <c r="F30" t="s" s="39">
-        <v>139</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1323,19 +1332,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
+        <v>139</v>
+      </c>
+      <c r="C31" t="s" s="31">
         <v>140</v>
       </c>
-      <c r="C31" t="s" s="31">
+      <c r="D31" t="s" s="32">
         <v>141</v>
       </c>
-      <c r="D31" t="s" s="32">
+      <c r="E31" t="s" s="33">
         <v>142</v>
       </c>
-      <c r="E31" t="s" s="33">
+      <c r="F31" t="s" s="34">
         <v>143</v>
-      </c>
-      <c r="F31" t="s" s="34">
-        <v>144</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1343,19 +1352,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
+        <v>144</v>
+      </c>
+      <c r="C32" t="s" s="36">
         <v>145</v>
-      </c>
-      <c r="C32" t="s" s="36">
-        <v>146</v>
       </c>
       <c r="D32" t="s" s="37">
         <v>146</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1363,19 +1372,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-08-01.xlsx
+++ b/past_data/site_8023/2026-08-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="154">
   <si>
     <t>No.</t>
   </si>
@@ -35,186 +35,189 @@
     <t>평균</t>
   </si>
   <si>
-    <t>372.4</t>
+    <t>362.6</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
+    <t>3.6</t>
+  </si>
+  <si>
+    <t>01일</t>
+  </si>
+  <si>
+    <t>453.6</t>
+  </si>
+  <si>
+    <t>4.5</t>
+  </si>
+  <si>
+    <t>02일</t>
+  </si>
+  <si>
+    <t>475.8</t>
+  </si>
+  <si>
+    <t>929.4</t>
+  </si>
+  <si>
+    <t>4.8</t>
+  </si>
+  <si>
+    <t>9.3</t>
+  </si>
+  <si>
+    <t>03일</t>
+  </si>
+  <si>
+    <t>515.6</t>
+  </si>
+  <si>
+    <t>1445.0</t>
+  </si>
+  <si>
+    <t>5.2</t>
+  </si>
+  <si>
+    <t>14.5</t>
+  </si>
+  <si>
+    <t>04일</t>
+  </si>
+  <si>
+    <t>537.3</t>
+  </si>
+  <si>
+    <t>1982.3</t>
+  </si>
+  <si>
+    <t>5.4</t>
+  </si>
+  <si>
+    <t>19.8</t>
+  </si>
+  <si>
+    <t>05일</t>
+  </si>
+  <si>
+    <t>489.8</t>
+  </si>
+  <si>
+    <t>2472.1</t>
+  </si>
+  <si>
+    <t>4.9</t>
+  </si>
+  <si>
+    <t>24.7</t>
+  </si>
+  <si>
+    <t>06일</t>
+  </si>
+  <si>
+    <t>540.1</t>
+  </si>
+  <si>
+    <t>3012.2</t>
+  </si>
+  <si>
+    <t>30.1</t>
+  </si>
+  <si>
+    <t>07일</t>
+  </si>
+  <si>
+    <t>523.4</t>
+  </si>
+  <si>
+    <t>3535.6</t>
+  </si>
+  <si>
+    <t>35.4</t>
+  </si>
+  <si>
+    <t>08일</t>
+  </si>
+  <si>
+    <t>482.2</t>
+  </si>
+  <si>
+    <t>4017.8</t>
+  </si>
+  <si>
+    <t>40.2</t>
+  </si>
+  <si>
+    <t>09일</t>
+  </si>
+  <si>
+    <t>392.0</t>
+  </si>
+  <si>
+    <t>4409.8</t>
+  </si>
+  <si>
+    <t>3.9</t>
+  </si>
+  <si>
+    <t>44.1</t>
+  </si>
+  <si>
+    <t>10일</t>
+  </si>
+  <si>
+    <t>460.3</t>
+  </si>
+  <si>
+    <t>4870.1</t>
+  </si>
+  <si>
+    <t>4.6</t>
+  </si>
+  <si>
+    <t>48.7</t>
+  </si>
+  <si>
+    <t>11일</t>
+  </si>
+  <si>
+    <t>477.7</t>
+  </si>
+  <si>
+    <t>5347.8</t>
+  </si>
+  <si>
+    <t>53.5</t>
+  </si>
+  <si>
+    <t>12일</t>
+  </si>
+  <si>
+    <t>558.0</t>
+  </si>
+  <si>
+    <t>5905.8</t>
+  </si>
+  <si>
+    <t>5.6</t>
+  </si>
+  <si>
+    <t>59.1</t>
+  </si>
+  <si>
+    <t>13일</t>
+  </si>
+  <si>
+    <t>365.1</t>
+  </si>
+  <si>
+    <t>6270.9</t>
+  </si>
+  <si>
     <t>3.7</t>
   </si>
   <si>
-    <t>01일</t>
-  </si>
-  <si>
-    <t>453.6</t>
-  </si>
-  <si>
-    <t>4.5</t>
-  </si>
-  <si>
-    <t>02일</t>
-  </si>
-  <si>
-    <t>475.8</t>
-  </si>
-  <si>
-    <t>929.4</t>
-  </si>
-  <si>
-    <t>4.8</t>
-  </si>
-  <si>
-    <t>9.3</t>
-  </si>
-  <si>
-    <t>03일</t>
-  </si>
-  <si>
-    <t>515.6</t>
-  </si>
-  <si>
-    <t>1445.0</t>
-  </si>
-  <si>
-    <t>5.2</t>
-  </si>
-  <si>
-    <t>14.5</t>
-  </si>
-  <si>
-    <t>04일</t>
-  </si>
-  <si>
-    <t>537.3</t>
-  </si>
-  <si>
-    <t>1982.3</t>
-  </si>
-  <si>
-    <t>5.4</t>
-  </si>
-  <si>
-    <t>19.8</t>
-  </si>
-  <si>
-    <t>05일</t>
-  </si>
-  <si>
-    <t>489.8</t>
-  </si>
-  <si>
-    <t>2472.1</t>
-  </si>
-  <si>
-    <t>4.9</t>
-  </si>
-  <si>
-    <t>24.7</t>
-  </si>
-  <si>
-    <t>06일</t>
-  </si>
-  <si>
-    <t>540.1</t>
-  </si>
-  <si>
-    <t>3012.2</t>
-  </si>
-  <si>
-    <t>30.1</t>
-  </si>
-  <si>
-    <t>07일</t>
-  </si>
-  <si>
-    <t>523.4</t>
-  </si>
-  <si>
-    <t>3535.6</t>
-  </si>
-  <si>
-    <t>35.4</t>
-  </si>
-  <si>
-    <t>08일</t>
-  </si>
-  <si>
-    <t>482.2</t>
-  </si>
-  <si>
-    <t>4017.8</t>
-  </si>
-  <si>
-    <t>40.2</t>
-  </si>
-  <si>
-    <t>09일</t>
-  </si>
-  <si>
-    <t>392.0</t>
-  </si>
-  <si>
-    <t>4409.8</t>
-  </si>
-  <si>
-    <t>3.9</t>
-  </si>
-  <si>
-    <t>44.1</t>
-  </si>
-  <si>
-    <t>10일</t>
-  </si>
-  <si>
-    <t>460.3</t>
-  </si>
-  <si>
-    <t>4870.1</t>
-  </si>
-  <si>
-    <t>4.6</t>
-  </si>
-  <si>
-    <t>48.7</t>
-  </si>
-  <si>
-    <t>11일</t>
-  </si>
-  <si>
-    <t>477.7</t>
-  </si>
-  <si>
-    <t>5347.8</t>
-  </si>
-  <si>
-    <t>53.5</t>
-  </si>
-  <si>
-    <t>12일</t>
-  </si>
-  <si>
-    <t>558.0</t>
-  </si>
-  <si>
-    <t>5905.8</t>
-  </si>
-  <si>
-    <t>5.6</t>
-  </si>
-  <si>
-    <t>59.1</t>
-  </si>
-  <si>
-    <t>13일</t>
-  </si>
-  <si>
-    <t>365.1</t>
-  </si>
-  <si>
-    <t>6270.9</t>
-  </si>
-  <si>
     <t>62.7</t>
   </si>
   <si>
@@ -299,9 +302,6 @@
     <t>7991.8</t>
   </si>
   <si>
-    <t>3.6</t>
-  </si>
-  <si>
     <t>79.9</t>
   </si>
   <si>
@@ -464,7 +464,16 @@
     <t>31일</t>
   </si>
   <si>
-    <t>0.0</t>
+    <t>70.6</t>
+  </si>
+  <si>
+    <t>11241.2</t>
+  </si>
+  <si>
+    <t>0.7</t>
+  </si>
+  <si>
+    <t>112.4</t>
   </si>
 </sst>
 </file>
@@ -1021,10 +1030,10 @@
         <v>66</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>9</v>
+        <v>67</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -1032,19 +1041,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -1052,19 +1061,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -1072,19 +1081,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -1092,19 +1101,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -1112,19 +1121,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E20" t="s" s="38">
         <v>21</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -1132,16 +1141,16 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>95</v>
+        <v>9</v>
       </c>
       <c r="F21" t="s" s="34">
         <v>96</v>
@@ -1378,13 +1387,13 @@
         <v>150</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
   </sheetData>
